--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -1859,42 +1859,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132116915</v>
+        <v>132115009</v>
       </c>
       <c r="B13" t="n">
-        <v>57909</v>
+        <v>80408</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1902,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781709</v>
+        <v>781643</v>
       </c>
       <c r="R13" t="n">
-        <v>7178098</v>
+        <v>7177977</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1937,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>färska typiska hack i gran</t>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,6 +1946,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,41 +1965,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132115729</v>
+        <v>132116228</v>
       </c>
       <c r="B14" t="n">
-        <v>83120</v>
+        <v>99052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2011,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781627</v>
+        <v>781649</v>
       </c>
       <c r="R14" t="n">
-        <v>7178004</v>
+        <v>7178072</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,37 +2071,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132115009</v>
+        <v>132116915</v>
       </c>
       <c r="B15" t="n">
-        <v>80408</v>
+        <v>57909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781643</v>
+        <v>781709</v>
       </c>
       <c r="R15" t="n">
-        <v>7177977</v>
+        <v>7178098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2154,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på en gammal sälg</t>
+          <t>färska typiska hack i gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,7 +2163,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2180,42 +2181,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132116228</v>
+        <v>132115729</v>
       </c>
       <c r="B16" t="n">
-        <v>99052</v>
+        <v>83120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781649</v>
+        <v>781627</v>
       </c>
       <c r="R16" t="n">
-        <v>7178072</v>
+        <v>7178004</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132115443</v>
+        <v>132116712</v>
       </c>
       <c r="B52" t="n">
-        <v>79274</v>
+        <v>57909</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6054,30 +6054,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6085,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>781657</v>
+        <v>781744</v>
       </c>
       <c r="R52" t="n">
-        <v>7178001</v>
+        <v>7178073</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6123,13 +6124,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6148,42 +6153,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132116712</v>
+        <v>132114938</v>
       </c>
       <c r="B53" t="n">
-        <v>57909</v>
+        <v>99052</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6191,10 +6196,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>781744</v>
+        <v>781627</v>
       </c>
       <c r="R53" t="n">
-        <v>7178073</v>
+        <v>7177962</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6229,17 +6234,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6258,42 +6259,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132114938</v>
+        <v>132115443</v>
       </c>
       <c r="B54" t="n">
-        <v>99052</v>
+        <v>79274</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>781627</v>
+        <v>781657</v>
       </c>
       <c r="R54" t="n">
-        <v>7177962</v>
+        <v>7178001</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>132116162</v>
       </c>
       <c r="B3" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132116033</v>
       </c>
       <c r="B4" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,42 +999,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132117131</v>
+        <v>132115035</v>
       </c>
       <c r="B5" t="n">
-        <v>99052</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781577</v>
+        <v>781656</v>
       </c>
       <c r="R5" t="n">
-        <v>7178033</v>
+        <v>7177972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1077,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på två granlågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,41 +1109,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132115035</v>
+        <v>132117131</v>
       </c>
       <c r="B6" t="n">
-        <v>91846</v>
+        <v>99054</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781656</v>
+        <v>781577</v>
       </c>
       <c r="R6" t="n">
-        <v>7177972</v>
+        <v>7178033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,11 +1188,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på två granlågor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1218,7 @@
         <v>132115952</v>
       </c>
       <c r="B7" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>132115712</v>
       </c>
       <c r="B8" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>132114881</v>
       </c>
       <c r="B9" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>132116022</v>
       </c>
       <c r="B10" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>132115520</v>
       </c>
       <c r="B11" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>132115561</v>
       </c>
       <c r="B12" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>132115009</v>
       </c>
       <c r="B13" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,42 +1965,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132116228</v>
+        <v>132115729</v>
       </c>
       <c r="B14" t="n">
-        <v>99052</v>
+        <v>83122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2008,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781649</v>
+        <v>781627</v>
       </c>
       <c r="R14" t="n">
-        <v>7178072</v>
+        <v>7178004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,42 +2070,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132116915</v>
+        <v>132116228</v>
       </c>
       <c r="B15" t="n">
-        <v>57909</v>
+        <v>99054</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2114,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781709</v>
+        <v>781649</v>
       </c>
       <c r="R15" t="n">
-        <v>7178098</v>
+        <v>7178072</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,17 +2151,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>färska typiska hack i gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2181,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132115729</v>
+        <v>132116915</v>
       </c>
       <c r="B16" t="n">
-        <v>83120</v>
+        <v>57911</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,30 +2187,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2223,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781627</v>
+        <v>781709</v>
       </c>
       <c r="R16" t="n">
-        <v>7178004</v>
+        <v>7178098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,13 +2257,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färska typiska hack i gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,42 +2286,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132114839</v>
+        <v>132116152</v>
       </c>
       <c r="B17" t="n">
-        <v>99052</v>
+        <v>79276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781551</v>
+        <v>781634</v>
       </c>
       <c r="R17" t="n">
-        <v>7177965</v>
+        <v>7178089</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,42 +2391,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132115248</v>
+        <v>132116069</v>
       </c>
       <c r="B18" t="n">
-        <v>99052</v>
+        <v>57914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2435,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781662</v>
+        <v>781642</v>
       </c>
       <c r="R18" t="n">
-        <v>7177984</v>
+        <v>7178096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,16 +2470,15 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2503,38 +2497,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132116069</v>
+        <v>132114839</v>
       </c>
       <c r="B19" t="n">
-        <v>57912</v>
+        <v>99054</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2542,10 +2540,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781642</v>
+        <v>781551</v>
       </c>
       <c r="R19" t="n">
-        <v>7178096</v>
+        <v>7177965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,17 +2578,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2609,41 +2603,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132116152</v>
+        <v>132115248</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>99054</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2651,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781634</v>
+        <v>781662</v>
       </c>
       <c r="R20" t="n">
-        <v>7178089</v>
+        <v>7177984</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,6 +2682,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132117060</v>
+        <v>132115308</v>
       </c>
       <c r="B21" t="n">
-        <v>57912</v>
+        <v>92036</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,31 +2725,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2757,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781577</v>
+        <v>781683</v>
       </c>
       <c r="R21" t="n">
-        <v>7178033</v>
+        <v>7177990</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,17 +2794,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2827,7 +2822,7 @@
         <v>132116701</v>
       </c>
       <c r="B22" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2928,7 @@
         <v>132115101</v>
       </c>
       <c r="B23" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,7 +3039,7 @@
         <v>132114890</v>
       </c>
       <c r="B24" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3150,7 +3145,7 @@
         <v>132115704</v>
       </c>
       <c r="B25" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3253,41 +3248,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132115308</v>
+        <v>132116490</v>
       </c>
       <c r="B26" t="n">
-        <v>92034</v>
+        <v>99054</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3295,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781683</v>
+        <v>781684</v>
       </c>
       <c r="R26" t="n">
-        <v>7177990</v>
+        <v>7178030</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3358,10 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132116478</v>
+        <v>132117060</v>
       </c>
       <c r="B27" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3391,7 +3387,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3401,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781686</v>
+        <v>781577</v>
       </c>
       <c r="R27" t="n">
-        <v>7178038</v>
+        <v>7178033</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,14 +3437,14 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>födosökande i granar</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3468,42 +3464,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132116490</v>
+        <v>132116478</v>
       </c>
       <c r="B28" t="n">
-        <v>99052</v>
+        <v>57914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3511,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781684</v>
+        <v>781686</v>
       </c>
       <c r="R28" t="n">
-        <v>7178030</v>
+        <v>7178038</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3549,13 +3545,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>födosökande i granar</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>132115227</v>
       </c>
       <c r="B29" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>132115000</v>
       </c>
       <c r="B30" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,10 +3786,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132116734</v>
+        <v>132114873</v>
       </c>
       <c r="B31" t="n">
-        <v>57909</v>
+        <v>91848</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,31 +3797,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3829,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781737</v>
+        <v>781574</v>
       </c>
       <c r="R31" t="n">
-        <v>7178076</v>
+        <v>7177976</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,17 +3866,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3896,41 +3891,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132114873</v>
+        <v>132115082</v>
       </c>
       <c r="B32" t="n">
-        <v>91846</v>
+        <v>99054</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3938,10 +3934,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>781574</v>
+        <v>781661</v>
       </c>
       <c r="R32" t="n">
-        <v>7177976</v>
+        <v>7177969</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4001,10 +3997,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132115082</v>
+        <v>132114818</v>
       </c>
       <c r="B33" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4044,10 +4040,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>781661</v>
+        <v>781549</v>
       </c>
       <c r="R33" t="n">
-        <v>7177969</v>
+        <v>7177957</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4080,6 +4076,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4107,42 +4108,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132114818</v>
+        <v>132116734</v>
       </c>
       <c r="B34" t="n">
-        <v>99052</v>
+        <v>57911</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4150,10 +4151,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781549</v>
+        <v>781737</v>
       </c>
       <c r="R34" t="n">
-        <v>7177957</v>
+        <v>7178076</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,7 +4191,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4199,7 +4200,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4218,42 +4218,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132114726</v>
+        <v>132115061</v>
       </c>
       <c r="B35" t="n">
-        <v>99052</v>
+        <v>92147</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4261,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781546</v>
+        <v>781656</v>
       </c>
       <c r="R35" t="n">
-        <v>7177958</v>
+        <v>7177972</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,6 +4296,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,41 +4328,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132115061</v>
+        <v>132114726</v>
       </c>
       <c r="B36" t="n">
-        <v>92145</v>
+        <v>99054</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4366,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781656</v>
+        <v>781546</v>
       </c>
       <c r="R36" t="n">
-        <v>7177972</v>
+        <v>7177958</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4402,11 +4407,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4437,7 +4437,7 @@
         <v>132116584</v>
       </c>
       <c r="B37" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>132115209</v>
       </c>
       <c r="B38" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4646,42 +4646,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132115870</v>
+        <v>132116218</v>
       </c>
       <c r="B39" t="n">
-        <v>99052</v>
+        <v>57911</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781624</v>
+        <v>781643</v>
       </c>
       <c r="R39" t="n">
-        <v>7178022</v>
+        <v>7178078</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,13 +4727,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4752,10 +4756,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132116829</v>
+        <v>132120397</v>
       </c>
       <c r="B40" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781713</v>
+        <v>781702</v>
       </c>
       <c r="R40" t="n">
-        <v>7178098</v>
+        <v>7178053</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4835,7 +4839,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4862,42 +4866,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132115918</v>
+        <v>132116829</v>
       </c>
       <c r="B41" t="n">
-        <v>99052</v>
+        <v>57914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4905,10 +4909,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>781592</v>
+        <v>781713</v>
       </c>
       <c r="R41" t="n">
-        <v>7178057</v>
+        <v>7178098</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,13 +4947,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4968,42 +4976,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132116218</v>
+        <v>132115870</v>
       </c>
       <c r="B42" t="n">
-        <v>57909</v>
+        <v>99054</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5011,10 +5019,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>781643</v>
+        <v>781624</v>
       </c>
       <c r="R42" t="n">
-        <v>7178078</v>
+        <v>7178022</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,17 +5057,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5078,42 +5082,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132120397</v>
+        <v>132115918</v>
       </c>
       <c r="B43" t="n">
-        <v>57912</v>
+        <v>99054</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5121,10 +5125,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>781702</v>
+        <v>781592</v>
       </c>
       <c r="R43" t="n">
-        <v>7178053</v>
+        <v>7178057</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,17 +5163,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>132116006</v>
       </c>
       <c r="B44" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>132115899</v>
       </c>
       <c r="B45" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>132115962</v>
       </c>
       <c r="B46" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>132116288</v>
       </c>
       <c r="B47" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>132116133</v>
       </c>
       <c r="B48" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>132116371</v>
       </c>
       <c r="B49" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>132115856</v>
       </c>
       <c r="B50" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>132115808</v>
       </c>
       <c r="B51" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132116712</v>
+        <v>132115443</v>
       </c>
       <c r="B52" t="n">
-        <v>57909</v>
+        <v>79276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6054,31 +6054,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6086,10 +6085,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>781744</v>
+        <v>781657</v>
       </c>
       <c r="R52" t="n">
-        <v>7178073</v>
+        <v>7178001</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6124,17 +6123,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6156,7 +6151,7 @@
         <v>132114938</v>
       </c>
       <c r="B53" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6259,10 +6254,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132115443</v>
+        <v>132116712</v>
       </c>
       <c r="B54" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6270,30 +6265,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6301,10 +6297,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>781657</v>
+        <v>781744</v>
       </c>
       <c r="R54" t="n">
-        <v>7178001</v>
+        <v>7178073</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6339,13 +6335,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>132114931</v>
       </c>
       <c r="B55" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6474,10 +6474,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132117193</v>
+        <v>132115371</v>
       </c>
       <c r="B56" t="n">
-        <v>57912</v>
+        <v>91848</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6485,27 +6485,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6513,10 +6516,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>781651</v>
+        <v>781688</v>
       </c>
       <c r="R56" t="n">
-        <v>7178085</v>
+        <v>7178003</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6551,17 +6554,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6580,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132114915</v>
+        <v>132117003</v>
       </c>
       <c r="B57" t="n">
-        <v>57909</v>
+        <v>91848</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6591,31 +6590,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6623,10 +6621,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>781609</v>
+        <v>781692</v>
       </c>
       <c r="R57" t="n">
-        <v>7177970</v>
+        <v>7178085</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,17 +6659,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>stort bohål i ihålig gammal asp</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6690,41 +6684,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132117003</v>
+        <v>132116952</v>
       </c>
       <c r="B58" t="n">
-        <v>91846</v>
+        <v>99054</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6732,10 +6727,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>781692</v>
+        <v>781696</v>
       </c>
       <c r="R58" t="n">
-        <v>7178085</v>
+        <v>7178090</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6795,42 +6790,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132116952</v>
+        <v>132114915</v>
       </c>
       <c r="B59" t="n">
-        <v>99052</v>
+        <v>57911</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6838,10 +6833,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>781696</v>
+        <v>781609</v>
       </c>
       <c r="R59" t="n">
-        <v>7178090</v>
+        <v>7177970</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6876,13 +6871,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>stort bohål i ihålig gammal asp</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6901,10 +6900,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132115371</v>
+        <v>132117193</v>
       </c>
       <c r="B60" t="n">
-        <v>91846</v>
+        <v>57914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6912,30 +6911,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6943,10 +6939,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>781688</v>
+        <v>781651</v>
       </c>
       <c r="R60" t="n">
-        <v>7178003</v>
+        <v>7178085</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6981,13 +6977,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132116569</v>
+        <v>132115934</v>
       </c>
       <c r="B61" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7017,31 +7017,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7049,10 +7048,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781705</v>
+        <v>781602</v>
       </c>
       <c r="R61" t="n">
-        <v>7178041</v>
+        <v>7178066</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7087,17 +7086,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7111,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132115934</v>
+        <v>132116569</v>
       </c>
       <c r="B62" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7127,30 +7122,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7158,10 +7154,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>781602</v>
+        <v>781705</v>
       </c>
       <c r="R62" t="n">
-        <v>7178066</v>
+        <v>7178041</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7196,13 +7192,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v>132115346</v>
       </c>
       <c r="B63" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7327,42 +7327,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132114698</v>
+        <v>132114993</v>
       </c>
       <c r="B64" t="n">
-        <v>57909</v>
+        <v>99054</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>781535</v>
+        <v>781633</v>
       </c>
       <c r="R64" t="n">
-        <v>7177946</v>
+        <v>7177971</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7408,17 +7408,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>bohål i tall</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7437,10 +7433,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132114993</v>
+        <v>132114700</v>
       </c>
       <c r="B65" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7480,10 +7476,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>781633</v>
+        <v>781545</v>
       </c>
       <c r="R65" t="n">
-        <v>7177971</v>
+        <v>7177946</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7543,10 +7539,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132116691</v>
+        <v>132114698</v>
       </c>
       <c r="B66" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7576,7 +7572,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7586,10 +7582,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>781724</v>
+        <v>781535</v>
       </c>
       <c r="R66" t="n">
-        <v>7178057</v>
+        <v>7177946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7622,6 +7618,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>bohål i tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7648,42 +7649,42 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132114700</v>
+        <v>132116691</v>
       </c>
       <c r="B67" t="n">
-        <v>99052</v>
+        <v>57911</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7691,10 +7692,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>781545</v>
+        <v>781724</v>
       </c>
       <c r="R67" t="n">
-        <v>7177946</v>
+        <v>7178057</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7736,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>132116300</v>
       </c>
       <c r="B68" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>132116723</v>
       </c>
       <c r="B69" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132115576</v>
+        <v>132115643</v>
       </c>
       <c r="B70" t="n">
-        <v>57912</v>
+        <v>80381</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7981,31 +7981,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8013,10 +8012,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>781656</v>
+        <v>781644</v>
       </c>
       <c r="R70" t="n">
-        <v>7178009</v>
+        <v>7178004</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8053,15 +8052,16 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8080,42 +8080,42 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132115737</v>
+        <v>132115576</v>
       </c>
       <c r="B71" t="n">
-        <v>99052</v>
+        <v>57914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>781633</v>
+        <v>781656</v>
       </c>
       <c r="R71" t="n">
-        <v>7178011</v>
+        <v>7178009</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8161,13 +8161,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8186,10 +8190,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132115643</v>
+        <v>132116562</v>
       </c>
       <c r="B72" t="n">
-        <v>80379</v>
+        <v>57914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8197,30 +8201,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8228,10 +8233,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>781644</v>
+        <v>781688</v>
       </c>
       <c r="R72" t="n">
-        <v>7178004</v>
+        <v>7178030</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8268,16 +8273,15 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>på en gammal sälg</t>
+          <t>typiska barksprätt</t>
         </is>
       </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8296,42 +8300,42 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132116562</v>
+        <v>132115737</v>
       </c>
       <c r="B73" t="n">
-        <v>57912</v>
+        <v>99054</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8339,10 +8343,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>781688</v>
+        <v>781633</v>
       </c>
       <c r="R73" t="n">
-        <v>7178030</v>
+        <v>7178011</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8377,17 +8381,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>typiska barksprätt</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132116162</v>
+        <v>132116033</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781632</v>
+        <v>781633</v>
       </c>
       <c r="R3" t="n">
-        <v>7178081</v>
+        <v>7178101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132116033</v>
+        <v>132116162</v>
       </c>
       <c r="B4" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781633</v>
+        <v>781632</v>
       </c>
       <c r="R4" t="n">
-        <v>7178101</v>
+        <v>7178081</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
         <v>132115035</v>
       </c>
       <c r="B5" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132117131</v>
+        <v>132115712</v>
       </c>
       <c r="B6" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781577</v>
+        <v>781622</v>
       </c>
       <c r="R6" t="n">
-        <v>7178033</v>
+        <v>7178004</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
         <v>132115952</v>
       </c>
       <c r="B7" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132115712</v>
+        <v>132117131</v>
       </c>
       <c r="B8" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781622</v>
+        <v>781577</v>
       </c>
       <c r="R8" t="n">
-        <v>7178004</v>
+        <v>7178033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1537,42 +1537,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132116022</v>
+        <v>132115561</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>91892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1580,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781624</v>
+        <v>781653</v>
       </c>
       <c r="R10" t="n">
-        <v>7178093</v>
+        <v>7178001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1645,7 @@
         <v>132115520</v>
       </c>
       <c r="B11" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,41 +1753,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132115561</v>
+        <v>132116022</v>
       </c>
       <c r="B12" t="n">
-        <v>91889</v>
+        <v>99098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781653</v>
+        <v>781624</v>
       </c>
       <c r="R12" t="n">
-        <v>7178001</v>
+        <v>7178093</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
         <v>132115729</v>
       </c>
       <c r="B13" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,42 +1964,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132116915</v>
+        <v>132115009</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>80451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781709</v>
+        <v>781643</v>
       </c>
       <c r="R14" t="n">
-        <v>7178098</v>
+        <v>7177977</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +2042,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska typiska hack i gran</t>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,6 +2051,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2074,37 +2070,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132115009</v>
+        <v>132116915</v>
       </c>
       <c r="B15" t="n">
-        <v>80449</v>
+        <v>57945</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781643</v>
+        <v>781709</v>
       </c>
       <c r="R15" t="n">
-        <v>7177977</v>
+        <v>7178098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,7 +2153,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på en gammal sälg</t>
+          <t>färska typiska hack i gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,7 +2162,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>132116228</v>
       </c>
       <c r="B16" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,42 +2286,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132114839</v>
+        <v>132116152</v>
       </c>
       <c r="B17" t="n">
-        <v>99095</v>
+        <v>79317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781551</v>
+        <v>781634</v>
       </c>
       <c r="R17" t="n">
-        <v>7177965</v>
+        <v>7178089</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2394,7 @@
         <v>132115248</v>
       </c>
       <c r="B18" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,38 +2502,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132116069</v>
+        <v>132114839</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2542,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781642</v>
+        <v>781551</v>
       </c>
       <c r="R19" t="n">
-        <v>7178096</v>
+        <v>7177965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,17 +2583,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2609,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132116152</v>
+        <v>132116069</v>
       </c>
       <c r="B20" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,30 +2619,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2651,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781634</v>
+        <v>781642</v>
       </c>
       <c r="R20" t="n">
-        <v>7178089</v>
+        <v>7178096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,13 +2685,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2714,42 +2714,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132115101</v>
+        <v>132115308</v>
       </c>
       <c r="B21" t="n">
-        <v>99095</v>
+        <v>92080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2757,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781657</v>
+        <v>781683</v>
       </c>
       <c r="R21" t="n">
-        <v>7177964</v>
+        <v>7177990</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,11 +2792,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>rikligt uppe på ett litet stenblock</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,42 +2819,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132114890</v>
+        <v>132117060</v>
       </c>
       <c r="B22" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2868,10 +2862,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781609</v>
+        <v>781577</v>
       </c>
       <c r="R22" t="n">
-        <v>7177971</v>
+        <v>7178033</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,13 +2900,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2931,42 +2929,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132115704</v>
+        <v>132116478</v>
       </c>
       <c r="B23" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2974,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781632</v>
+        <v>781686</v>
       </c>
       <c r="R23" t="n">
-        <v>7178004</v>
+        <v>7178038</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,13 +3010,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>födosökande i granar</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3037,41 +3039,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132115308</v>
+        <v>132116701</v>
       </c>
       <c r="B24" t="n">
-        <v>92077</v>
+        <v>99098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3079,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781683</v>
+        <v>781744</v>
       </c>
       <c r="R24" t="n">
-        <v>7177990</v>
+        <v>7178071</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,42 +3145,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132117060</v>
+        <v>132115704</v>
       </c>
       <c r="B25" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3185,10 +3188,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781577</v>
+        <v>781632</v>
       </c>
       <c r="R25" t="n">
-        <v>7178033</v>
+        <v>7178004</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,17 +3226,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3252,42 +3251,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132116478</v>
+        <v>132114890</v>
       </c>
       <c r="B26" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3295,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781686</v>
+        <v>781609</v>
       </c>
       <c r="R26" t="n">
-        <v>7178038</v>
+        <v>7177971</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,17 +3332,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>födosökande i granar</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3362,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132116701</v>
+        <v>132116490</v>
       </c>
       <c r="B27" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781744</v>
+        <v>781684</v>
       </c>
       <c r="R27" t="n">
-        <v>7178071</v>
+        <v>7178030</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,10 +3463,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132116490</v>
+        <v>132115101</v>
       </c>
       <c r="B28" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781684</v>
+        <v>781657</v>
       </c>
       <c r="R28" t="n">
-        <v>7178030</v>
+        <v>7177964</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3547,6 +3542,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>rikligt uppe på ett litet stenblock</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,7 +3577,7 @@
         <v>132115227</v>
       </c>
       <c r="B29" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>132115000</v>
       </c>
       <c r="B30" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,41 +3786,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132114873</v>
+        <v>132114818</v>
       </c>
       <c r="B31" t="n">
-        <v>91889</v>
+        <v>99098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3828,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781574</v>
+        <v>781549</v>
       </c>
       <c r="R31" t="n">
-        <v>7177976</v>
+        <v>7177957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3864,6 +3865,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3894,7 +3900,7 @@
         <v>132115082</v>
       </c>
       <c r="B32" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3997,42 +4003,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132114818</v>
+        <v>132114873</v>
       </c>
       <c r="B33" t="n">
-        <v>99095</v>
+        <v>91892</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4040,10 +4045,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>781549</v>
+        <v>781574</v>
       </c>
       <c r="R33" t="n">
-        <v>7177957</v>
+        <v>7177976</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,11 +4081,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4218,42 +4218,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132114726</v>
+        <v>132115061</v>
       </c>
       <c r="B35" t="n">
-        <v>99095</v>
+        <v>92191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4261,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781546</v>
+        <v>781656</v>
       </c>
       <c r="R35" t="n">
-        <v>7177958</v>
+        <v>7177972</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,6 +4296,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132116584</v>
+        <v>132115209</v>
       </c>
       <c r="B36" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781716</v>
+        <v>781663</v>
       </c>
       <c r="R36" t="n">
-        <v>7178070</v>
+        <v>7177982</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,10 +4434,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132115209</v>
+        <v>132116584</v>
       </c>
       <c r="B37" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4473,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>781663</v>
+        <v>781716</v>
       </c>
       <c r="R37" t="n">
-        <v>7177982</v>
+        <v>7178070</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4536,41 +4540,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132115061</v>
+        <v>132114726</v>
       </c>
       <c r="B38" t="n">
-        <v>92188</v>
+        <v>99098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4578,10 +4583,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>781656</v>
+        <v>781546</v>
       </c>
       <c r="R38" t="n">
-        <v>7177972</v>
+        <v>7177958</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,11 +4619,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,42 +4646,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132116218</v>
+        <v>132115870</v>
       </c>
       <c r="B39" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781643</v>
+        <v>781624</v>
       </c>
       <c r="R39" t="n">
-        <v>7178078</v>
+        <v>7178022</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,17 +4727,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4756,42 +4752,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132116829</v>
+        <v>132115918</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4799,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781713</v>
+        <v>781592</v>
       </c>
       <c r="R40" t="n">
-        <v>7178098</v>
+        <v>7178057</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4837,17 +4833,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4866,7 +4858,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132120397</v>
+        <v>132116829</v>
       </c>
       <c r="B41" t="n">
         <v>57948</v>
@@ -4909,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>781702</v>
+        <v>781713</v>
       </c>
       <c r="R41" t="n">
-        <v>7178053</v>
+        <v>7178098</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4949,7 +4941,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4976,42 +4968,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132115870</v>
+        <v>132120397</v>
       </c>
       <c r="B42" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5019,10 +5011,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>781624</v>
+        <v>781702</v>
       </c>
       <c r="R42" t="n">
-        <v>7178022</v>
+        <v>7178053</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5057,13 +5049,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5082,42 +5078,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132115918</v>
+        <v>132116218</v>
       </c>
       <c r="B43" t="n">
-        <v>99095</v>
+        <v>57945</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5125,10 +5121,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>781592</v>
+        <v>781643</v>
       </c>
       <c r="R43" t="n">
-        <v>7178057</v>
+        <v>7178078</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,13 +5159,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>132116288</v>
       </c>
       <c r="B44" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132116006</v>
+        <v>132115962</v>
       </c>
       <c r="B45" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>781602</v>
+        <v>781591</v>
       </c>
       <c r="R45" t="n">
-        <v>7178094</v>
+        <v>7178081</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,10 +5399,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132115899</v>
+        <v>132116006</v>
       </c>
       <c r="B46" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>781608</v>
+        <v>781602</v>
       </c>
       <c r="R46" t="n">
-        <v>7178045</v>
+        <v>7178094</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132115962</v>
+        <v>132115899</v>
       </c>
       <c r="B47" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>781591</v>
+        <v>781608</v>
       </c>
       <c r="R47" t="n">
-        <v>7178081</v>
+        <v>7178045</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5611,42 +5611,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132115856</v>
+        <v>132116133</v>
       </c>
       <c r="B48" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>781632</v>
+        <v>781637</v>
       </c>
       <c r="R48" t="n">
-        <v>7178016</v>
+        <v>7178091</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5692,13 +5692,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>observerad på nära håll vid födosök</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5717,42 +5721,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132115808</v>
+        <v>132116371</v>
       </c>
       <c r="B49" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5760,10 +5764,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>781627</v>
+        <v>781671</v>
       </c>
       <c r="R49" t="n">
-        <v>7178015</v>
+        <v>7178082</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5798,13 +5802,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>födosökande, observerad på ca 5 meters håll</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5823,42 +5831,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132116133</v>
+        <v>132115856</v>
       </c>
       <c r="B50" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5866,10 +5874,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>781637</v>
+        <v>781632</v>
       </c>
       <c r="R50" t="n">
-        <v>7178091</v>
+        <v>7178016</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,17 +5912,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>observerad på nära håll vid födosök</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5933,42 +5937,42 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132116371</v>
+        <v>132115808</v>
       </c>
       <c r="B51" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5976,10 +5980,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>781671</v>
+        <v>781627</v>
       </c>
       <c r="R51" t="n">
-        <v>7178082</v>
+        <v>7178015</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6014,17 +6018,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>födosökande, observerad på ca 5 meters håll</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6043,42 +6043,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132114938</v>
+        <v>132115443</v>
       </c>
       <c r="B52" t="n">
-        <v>99095</v>
+        <v>79317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6086,10 +6085,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>781627</v>
+        <v>781657</v>
       </c>
       <c r="R52" t="n">
-        <v>7177962</v>
+        <v>7178001</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6149,7 +6148,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132114931</v>
+        <v>132116712</v>
       </c>
       <c r="B53" t="n">
         <v>57945</v>
@@ -6182,7 +6181,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6192,10 +6191,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>781630</v>
+        <v>781744</v>
       </c>
       <c r="R53" t="n">
-        <v>7177957</v>
+        <v>7178073</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6232,7 +6231,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>hack i två lågor</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6259,7 +6258,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132116712</v>
+        <v>132114931</v>
       </c>
       <c r="B54" t="n">
         <v>57945</v>
@@ -6292,7 +6291,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6302,10 +6301,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>781744</v>
+        <v>781630</v>
       </c>
       <c r="R54" t="n">
-        <v>7178073</v>
+        <v>7177957</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6342,7 +6341,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>hack i två lågor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6369,41 +6368,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132115443</v>
+        <v>132114938</v>
       </c>
       <c r="B55" t="n">
-        <v>79315</v>
+        <v>99098</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>781657</v>
+        <v>781627</v>
       </c>
       <c r="R55" t="n">
-        <v>7178001</v>
+        <v>7177962</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6474,10 +6474,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132117193</v>
+        <v>132117003</v>
       </c>
       <c r="B56" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6485,27 +6485,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6513,7 +6516,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>781651</v>
+        <v>781692</v>
       </c>
       <c r="R56" t="n">
         <v>7178085</v>
@@ -6551,17 +6554,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6580,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132117003</v>
+        <v>132115371</v>
       </c>
       <c r="B57" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6622,10 +6621,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>781692</v>
+        <v>781688</v>
       </c>
       <c r="R57" t="n">
-        <v>7178085</v>
+        <v>7178003</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6685,10 +6684,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132115371</v>
+        <v>132114915</v>
       </c>
       <c r="B58" t="n">
-        <v>91889</v>
+        <v>57945</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6696,30 +6695,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>781688</v>
+        <v>781609</v>
       </c>
       <c r="R58" t="n">
-        <v>7178003</v>
+        <v>7177970</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,13 +6765,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>stort bohål i ihålig gammal asp</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6790,10 +6794,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132114915</v>
+        <v>132117193</v>
       </c>
       <c r="B59" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6801,16 +6805,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6821,11 +6825,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>781609</v>
+        <v>781651</v>
       </c>
       <c r="R59" t="n">
-        <v>7177970</v>
+        <v>7178085</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6873,14 +6873,14 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>stort bohål i ihålig gammal asp</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG59" t="b">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>132116952</v>
       </c>
       <c r="B60" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7006,42 +7006,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132116569</v>
+        <v>132115346</v>
       </c>
       <c r="B61" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781705</v>
+        <v>781690</v>
       </c>
       <c r="R61" t="n">
-        <v>7178041</v>
+        <v>7177998</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7087,17 +7087,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7119,7 +7115,7 @@
         <v>132115934</v>
       </c>
       <c r="B62" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7221,42 +7217,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132115346</v>
+        <v>132116569</v>
       </c>
       <c r="B63" t="n">
-        <v>99095</v>
+        <v>57948</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7264,10 +7260,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>781690</v>
+        <v>781705</v>
       </c>
       <c r="R63" t="n">
-        <v>7177998</v>
+        <v>7178041</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7302,13 +7298,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7327,7 +7327,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132116691</v>
+        <v>132114698</v>
       </c>
       <c r="B64" t="n">
         <v>57945</v>
@@ -7360,7 +7360,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>781724</v>
+        <v>781535</v>
       </c>
       <c r="R64" t="n">
-        <v>7178057</v>
+        <v>7177946</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7406,6 +7406,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>bohål i tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,42 +7437,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132114698</v>
+        <v>132114700</v>
       </c>
       <c r="B65" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7475,7 +7480,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>781535</v>
+        <v>781545</v>
       </c>
       <c r="R65" t="n">
         <v>7177946</v>
@@ -7513,17 +7518,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>bohål i tall</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7545,7 +7546,7 @@
         <v>132114993</v>
       </c>
       <c r="B66" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7648,42 +7649,42 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132114700</v>
+        <v>132116691</v>
       </c>
       <c r="B67" t="n">
-        <v>99095</v>
+        <v>57945</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7691,10 +7692,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>781545</v>
+        <v>781724</v>
       </c>
       <c r="R67" t="n">
-        <v>7177946</v>
+        <v>7178057</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7736,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>132116300</v>
       </c>
       <c r="B68" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>132115643</v>
       </c>
       <c r="B72" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>132115737</v>
       </c>
       <c r="B73" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -2286,41 +2286,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132116152</v>
+        <v>132115248</v>
       </c>
       <c r="B17" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2328,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781634</v>
+        <v>781662</v>
       </c>
       <c r="R17" t="n">
-        <v>7178089</v>
+        <v>7177984</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2364,6 +2365,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132115248</v>
+        <v>132114839</v>
       </c>
       <c r="B18" t="n">
         <v>99098</v>
@@ -2434,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781662</v>
+        <v>781551</v>
       </c>
       <c r="R18" t="n">
-        <v>7177984</v>
+        <v>7177965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,11 +2476,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,42 +2503,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132114839</v>
+        <v>132116152</v>
       </c>
       <c r="B19" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781551</v>
+        <v>781634</v>
       </c>
       <c r="R19" t="n">
-        <v>7177965</v>
+        <v>7178089</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132115870</v>
+        <v>132115918</v>
       </c>
       <c r="B39" t="n">
         <v>99098</v>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781624</v>
+        <v>781592</v>
       </c>
       <c r="R39" t="n">
-        <v>7178022</v>
+        <v>7178057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4752,7 +4752,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132115918</v>
+        <v>132115870</v>
       </c>
       <c r="B40" t="n">
         <v>99098</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781592</v>
+        <v>781624</v>
       </c>
       <c r="R40" t="n">
-        <v>7178057</v>
+        <v>7178022</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132116829</v>
+        <v>132116218</v>
       </c>
       <c r="B41" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4869,16 +4869,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>781713</v>
+        <v>781643</v>
       </c>
       <c r="R41" t="n">
-        <v>7178098</v>
+        <v>7178078</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4941,14 +4941,14 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132120397</v>
+        <v>132116829</v>
       </c>
       <c r="B42" t="n">
         <v>57948</v>
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>781702</v>
+        <v>781713</v>
       </c>
       <c r="R42" t="n">
-        <v>7178053</v>
+        <v>7178098</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5078,10 +5078,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132116218</v>
+        <v>132120397</v>
       </c>
       <c r="B43" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5089,16 +5089,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>781643</v>
+        <v>781702</v>
       </c>
       <c r="R43" t="n">
-        <v>7178078</v>
+        <v>7178053</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5161,14 +5161,14 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132115443</v>
+        <v>132116712</v>
       </c>
       <c r="B52" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6054,30 +6054,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6085,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>781657</v>
+        <v>781744</v>
       </c>
       <c r="R52" t="n">
-        <v>7178001</v>
+        <v>7178073</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6123,13 +6124,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6148,7 +6153,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132116712</v>
+        <v>132114931</v>
       </c>
       <c r="B53" t="n">
         <v>57945</v>
@@ -6181,7 +6186,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6191,10 +6196,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>781744</v>
+        <v>781630</v>
       </c>
       <c r="R53" t="n">
-        <v>7178073</v>
+        <v>7177957</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6231,7 +6236,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>hack i två lågor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6258,10 +6263,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132114931</v>
+        <v>132115443</v>
       </c>
       <c r="B54" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6269,31 +6274,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6301,10 +6305,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>781630</v>
+        <v>781657</v>
       </c>
       <c r="R54" t="n">
-        <v>7177957</v>
+        <v>7178001</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6339,17 +6343,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>hack i två lågor</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7006,42 +7006,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132115346</v>
+        <v>132116569</v>
       </c>
       <c r="B61" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781690</v>
+        <v>781705</v>
       </c>
       <c r="R61" t="n">
-        <v>7177998</v>
+        <v>7178041</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7087,13 +7087,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7217,42 +7221,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132116569</v>
+        <v>132115346</v>
       </c>
       <c r="B63" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7260,10 +7264,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>781705</v>
+        <v>781690</v>
       </c>
       <c r="R63" t="n">
-        <v>7178041</v>
+        <v>7177998</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7298,17 +7302,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7327,7 +7327,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132114698</v>
+        <v>132116691</v>
       </c>
       <c r="B64" t="n">
         <v>57945</v>
@@ -7360,7 +7360,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>781535</v>
+        <v>781724</v>
       </c>
       <c r="R64" t="n">
-        <v>7177946</v>
+        <v>7178057</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7406,11 +7406,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>bohål i tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7437,42 +7432,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132114700</v>
+        <v>132114698</v>
       </c>
       <c r="B65" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7480,7 +7475,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>781545</v>
+        <v>781535</v>
       </c>
       <c r="R65" t="n">
         <v>7177946</v>
@@ -7518,13 +7513,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>bohål i tall</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7543,7 +7542,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132114993</v>
+        <v>132114700</v>
       </c>
       <c r="B66" t="n">
         <v>99098</v>
@@ -7586,10 +7585,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>781633</v>
+        <v>781545</v>
       </c>
       <c r="R66" t="n">
-        <v>7177971</v>
+        <v>7177946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7649,42 +7648,42 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132116691</v>
+        <v>132114993</v>
       </c>
       <c r="B67" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7692,10 +7691,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>781724</v>
+        <v>781633</v>
       </c>
       <c r="R67" t="n">
-        <v>7178057</v>
+        <v>7177971</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7736,6 +7735,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -6474,41 +6474,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132117003</v>
+        <v>132116952</v>
       </c>
       <c r="B56" t="n">
-        <v>91892</v>
+        <v>99098</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6516,10 +6517,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>781692</v>
+        <v>781696</v>
       </c>
       <c r="R56" t="n">
-        <v>7178085</v>
+        <v>7178090</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6579,7 +6580,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132115371</v>
+        <v>132117003</v>
       </c>
       <c r="B57" t="n">
         <v>91892</v>
@@ -6621,10 +6622,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>781688</v>
+        <v>781692</v>
       </c>
       <c r="R57" t="n">
-        <v>7178003</v>
+        <v>7178085</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6684,10 +6685,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132114915</v>
+        <v>132115371</v>
       </c>
       <c r="B58" t="n">
-        <v>57945</v>
+        <v>91892</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6695,31 +6696,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>781609</v>
+        <v>781688</v>
       </c>
       <c r="R58" t="n">
-        <v>7177970</v>
+        <v>7178003</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,17 +6765,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>stort bohål i ihålig gammal asp</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6794,10 +6790,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132117193</v>
+        <v>132114915</v>
       </c>
       <c r="B59" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6805,16 +6801,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6825,7 +6821,11 @@
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>781651</v>
+        <v>781609</v>
       </c>
       <c r="R59" t="n">
-        <v>7178085</v>
+        <v>7177970</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6873,14 +6873,14 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>stort bohål i ihålig gammal asp</t>
         </is>
       </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="b">
         <v>0</v>
@@ -6900,42 +6900,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132116952</v>
+        <v>132117193</v>
       </c>
       <c r="B60" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6943,10 +6939,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>781696</v>
+        <v>781651</v>
       </c>
       <c r="R60" t="n">
-        <v>7178090</v>
+        <v>7178085</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6981,13 +6977,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7006,42 +7006,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132116569</v>
+        <v>132115346</v>
       </c>
       <c r="B61" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781705</v>
+        <v>781690</v>
       </c>
       <c r="R61" t="n">
-        <v>7178041</v>
+        <v>7177998</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7087,17 +7087,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7221,42 +7217,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132115346</v>
+        <v>132116569</v>
       </c>
       <c r="B63" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7264,10 +7260,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>781690</v>
+        <v>781705</v>
       </c>
       <c r="R63" t="n">
-        <v>7177998</v>
+        <v>7178041</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7302,13 +7298,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7327,7 +7327,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132116691</v>
+        <v>132114698</v>
       </c>
       <c r="B64" t="n">
         <v>57945</v>
@@ -7360,7 +7360,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>781724</v>
+        <v>781535</v>
       </c>
       <c r="R64" t="n">
-        <v>7178057</v>
+        <v>7177946</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7406,6 +7406,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>bohål i tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7432,7 +7437,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132114698</v>
+        <v>132116691</v>
       </c>
       <c r="B65" t="n">
         <v>57945</v>
@@ -7465,7 +7470,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7475,10 +7480,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>781535</v>
+        <v>781724</v>
       </c>
       <c r="R65" t="n">
-        <v>7177946</v>
+        <v>7178057</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7511,11 +7516,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>bohål i tall</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -675,43 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132120235</v>
+        <v>132116162</v>
       </c>
       <c r="B2" t="n">
-        <v>5179</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781536</v>
+        <v>781632</v>
       </c>
       <c r="R2" t="n">
-        <v>7177982</v>
+        <v>7178081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>typiska gnagspår på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -893,42 +887,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132116162</v>
+        <v>132120235</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781632</v>
+        <v>781536</v>
       </c>
       <c r="R4" t="n">
-        <v>7178081</v>
+        <v>7177982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>typiska gnagspår på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132115712</v>
+        <v>132117131</v>
       </c>
       <c r="B6" t="n">
         <v>99098</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781622</v>
+        <v>781577</v>
       </c>
       <c r="R6" t="n">
-        <v>7178004</v>
+        <v>7178033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132117131</v>
+        <v>132115712</v>
       </c>
       <c r="B8" t="n">
         <v>99098</v>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781577</v>
+        <v>781622</v>
       </c>
       <c r="R8" t="n">
-        <v>7178033</v>
+        <v>7178004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132115520</v>
+        <v>132116022</v>
       </c>
       <c r="B11" t="n">
         <v>99098</v>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781655</v>
+        <v>781624</v>
       </c>
       <c r="R11" t="n">
-        <v>7178001</v>
+        <v>7178093</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,11 +1721,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,7 +1748,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132116022</v>
+        <v>132115520</v>
       </c>
       <c r="B12" t="n">
         <v>99098</v>
@@ -1796,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781624</v>
+        <v>781655</v>
       </c>
       <c r="R12" t="n">
-        <v>7178093</v>
+        <v>7178001</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,6 +1827,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132115729</v>
+        <v>132116915</v>
       </c>
       <c r="B13" t="n">
-        <v>83163</v>
+        <v>57945</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,30 +1870,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1901,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781627</v>
+        <v>781709</v>
       </c>
       <c r="R13" t="n">
-        <v>7178004</v>
+        <v>7178098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,13 +1940,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska typiska hack i gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1964,36 +1969,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132115009</v>
+        <v>132115729</v>
       </c>
       <c r="B14" t="n">
-        <v>80451</v>
+        <v>83163</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2002,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781643</v>
+        <v>781627</v>
       </c>
       <c r="R14" t="n">
-        <v>7177977</v>
+        <v>7178004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,11 +2047,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,42 +2074,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132116915</v>
+        <v>132115009</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>80451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2113,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781709</v>
+        <v>781643</v>
       </c>
       <c r="R15" t="n">
-        <v>7178098</v>
+        <v>7177977</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2152,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska typiska hack i gran</t>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,6 +2161,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2286,42 +2286,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132115248</v>
+        <v>132116069</v>
       </c>
       <c r="B17" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781662</v>
+        <v>781642</v>
       </c>
       <c r="R17" t="n">
-        <v>7177984</v>
+        <v>7178096</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,16 +2365,15 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2397,42 +2392,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132114839</v>
+        <v>132116152</v>
       </c>
       <c r="B18" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2440,10 +2434,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781551</v>
+        <v>781634</v>
       </c>
       <c r="R18" t="n">
-        <v>7177965</v>
+        <v>7178089</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,41 +2497,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132116152</v>
+        <v>132114839</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2545,10 +2540,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781634</v>
+        <v>781551</v>
       </c>
       <c r="R19" t="n">
-        <v>7178089</v>
+        <v>7177965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2608,38 +2603,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132116069</v>
+        <v>132115248</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2647,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781642</v>
+        <v>781662</v>
       </c>
       <c r="R20" t="n">
-        <v>7178096</v>
+        <v>7177984</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,15 +2686,16 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2714,41 +2714,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132115308</v>
+        <v>132116701</v>
       </c>
       <c r="B21" t="n">
-        <v>92080</v>
+        <v>99098</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2756,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781683</v>
+        <v>781744</v>
       </c>
       <c r="R21" t="n">
-        <v>7177990</v>
+        <v>7178071</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2819,42 +2820,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132117060</v>
+        <v>132115101</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2862,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781577</v>
+        <v>781657</v>
       </c>
       <c r="R22" t="n">
-        <v>7178033</v>
+        <v>7177964</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,15 +2903,16 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>rikligt uppe på ett litet stenblock</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2929,42 +2931,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132116478</v>
+        <v>132114890</v>
       </c>
       <c r="B23" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2972,10 +2974,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781686</v>
+        <v>781609</v>
       </c>
       <c r="R23" t="n">
-        <v>7178038</v>
+        <v>7177971</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3010,17 +3012,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>födosökande i granar</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3039,7 +3037,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132116701</v>
+        <v>132115704</v>
       </c>
       <c r="B24" t="n">
         <v>99098</v>
@@ -3082,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781744</v>
+        <v>781632</v>
       </c>
       <c r="R24" t="n">
-        <v>7178071</v>
+        <v>7178004</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3143,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132115704</v>
+        <v>132116490</v>
       </c>
       <c r="B25" t="n">
         <v>99098</v>
@@ -3188,10 +3186,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781632</v>
+        <v>781684</v>
       </c>
       <c r="R25" t="n">
-        <v>7178004</v>
+        <v>7178030</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,42 +3249,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132114890</v>
+        <v>132115308</v>
       </c>
       <c r="B26" t="n">
-        <v>99098</v>
+        <v>92080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3294,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781609</v>
+        <v>781683</v>
       </c>
       <c r="R26" t="n">
-        <v>7177971</v>
+        <v>7177990</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,42 +3354,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132116490</v>
+        <v>132117060</v>
       </c>
       <c r="B27" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3400,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781684</v>
+        <v>781577</v>
       </c>
       <c r="R27" t="n">
-        <v>7178030</v>
+        <v>7178033</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3438,13 +3435,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3463,42 +3464,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132115101</v>
+        <v>132116478</v>
       </c>
       <c r="B28" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3506,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781657</v>
+        <v>781686</v>
       </c>
       <c r="R28" t="n">
-        <v>7177964</v>
+        <v>7178038</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3546,7 +3547,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>rikligt uppe på ett litet stenblock</t>
+          <t>födosökande i granar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3555,7 +3556,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3786,42 +3786,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132114818</v>
+        <v>132114873</v>
       </c>
       <c r="B31" t="n">
-        <v>99098</v>
+        <v>91892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3829,10 +3828,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781549</v>
+        <v>781574</v>
       </c>
       <c r="R31" t="n">
-        <v>7177957</v>
+        <v>7177976</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3865,11 +3864,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4003,41 +3997,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132114873</v>
+        <v>132114818</v>
       </c>
       <c r="B33" t="n">
-        <v>91892</v>
+        <v>99098</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4045,10 +4040,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>781574</v>
+        <v>781549</v>
       </c>
       <c r="R33" t="n">
-        <v>7177976</v>
+        <v>7177957</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4081,6 +4076,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4218,41 +4218,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132115061</v>
+        <v>132114726</v>
       </c>
       <c r="B35" t="n">
-        <v>92191</v>
+        <v>99098</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4260,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781656</v>
+        <v>781546</v>
       </c>
       <c r="R35" t="n">
-        <v>7177972</v>
+        <v>7177958</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,11 +4297,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4328,7 +4324,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132115209</v>
+        <v>132116584</v>
       </c>
       <c r="B36" t="n">
         <v>99098</v>
@@ -4371,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781663</v>
+        <v>781716</v>
       </c>
       <c r="R36" t="n">
-        <v>7177982</v>
+        <v>7178070</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4434,7 +4430,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132116584</v>
+        <v>132115209</v>
       </c>
       <c r="B37" t="n">
         <v>99098</v>
@@ -4477,10 +4473,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>781716</v>
+        <v>781663</v>
       </c>
       <c r="R37" t="n">
-        <v>7178070</v>
+        <v>7177982</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,42 +4536,41 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132114726</v>
+        <v>132115061</v>
       </c>
       <c r="B38" t="n">
-        <v>99098</v>
+        <v>92191</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4583,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>781546</v>
+        <v>781656</v>
       </c>
       <c r="R38" t="n">
-        <v>7177958</v>
+        <v>7177972</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4619,6 +4614,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,42 +4646,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132115918</v>
+        <v>132116829</v>
       </c>
       <c r="B39" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781592</v>
+        <v>781713</v>
       </c>
       <c r="R39" t="n">
-        <v>7178057</v>
+        <v>7178098</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,13 +4727,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4752,42 +4756,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132115870</v>
+        <v>132120397</v>
       </c>
       <c r="B40" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4795,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781624</v>
+        <v>781702</v>
       </c>
       <c r="R40" t="n">
-        <v>7178022</v>
+        <v>7178053</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4833,13 +4837,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4968,42 +4976,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132116829</v>
+        <v>132115870</v>
       </c>
       <c r="B42" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5011,10 +5019,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>781713</v>
+        <v>781624</v>
       </c>
       <c r="R42" t="n">
-        <v>7178098</v>
+        <v>7178022</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,17 +5057,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5078,42 +5082,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132120397</v>
+        <v>132115918</v>
       </c>
       <c r="B43" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5121,10 +5125,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>781702</v>
+        <v>781592</v>
       </c>
       <c r="R43" t="n">
-        <v>7178053</v>
+        <v>7178057</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,17 +5163,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5188,41 +5188,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132116288</v>
+        <v>132116006</v>
       </c>
       <c r="B44" t="n">
-        <v>91892</v>
+        <v>99098</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5230,10 +5231,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>781649</v>
+        <v>781602</v>
       </c>
       <c r="R44" t="n">
-        <v>7178072</v>
+        <v>7178094</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,7 +5294,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132115962</v>
+        <v>132115899</v>
       </c>
       <c r="B45" t="n">
         <v>99098</v>
@@ -5336,10 +5337,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>781591</v>
+        <v>781608</v>
       </c>
       <c r="R45" t="n">
-        <v>7178081</v>
+        <v>7178045</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,7 +5400,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132116006</v>
+        <v>132115962</v>
       </c>
       <c r="B46" t="n">
         <v>99098</v>
@@ -5442,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>781602</v>
+        <v>781591</v>
       </c>
       <c r="R46" t="n">
-        <v>7178094</v>
+        <v>7178081</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5505,42 +5506,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132115899</v>
+        <v>132116288</v>
       </c>
       <c r="B47" t="n">
-        <v>99098</v>
+        <v>91892</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>781608</v>
+        <v>781649</v>
       </c>
       <c r="R47" t="n">
-        <v>7178045</v>
+        <v>7178072</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6043,10 +6043,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132116712</v>
+        <v>132115443</v>
       </c>
       <c r="B52" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6054,31 +6054,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6086,10 +6085,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>781744</v>
+        <v>781657</v>
       </c>
       <c r="R52" t="n">
-        <v>7178073</v>
+        <v>7178001</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6124,17 +6123,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6153,7 +6148,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132114931</v>
+        <v>132116712</v>
       </c>
       <c r="B53" t="n">
         <v>57945</v>
@@ -6186,7 +6181,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6196,10 +6191,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>781630</v>
+        <v>781744</v>
       </c>
       <c r="R53" t="n">
-        <v>7177957</v>
+        <v>7178073</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6236,7 +6231,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>hack i två lågor</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6263,10 +6258,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132115443</v>
+        <v>132114931</v>
       </c>
       <c r="B54" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6274,30 +6269,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6305,10 +6301,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>781657</v>
+        <v>781630</v>
       </c>
       <c r="R54" t="n">
-        <v>7178001</v>
+        <v>7177957</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6343,13 +6339,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>hack i två lågor</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6474,42 +6474,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132116952</v>
+        <v>132117193</v>
       </c>
       <c r="B56" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6517,10 +6513,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>781696</v>
+        <v>781651</v>
       </c>
       <c r="R56" t="n">
-        <v>7178090</v>
+        <v>7178085</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6555,13 +6551,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6900,38 +6900,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132117193</v>
+        <v>132116952</v>
       </c>
       <c r="B60" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6939,10 +6943,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>781651</v>
+        <v>781696</v>
       </c>
       <c r="R60" t="n">
-        <v>7178085</v>
+        <v>7178090</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,17 +6981,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7006,42 +7006,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132115346</v>
+        <v>132116569</v>
       </c>
       <c r="B61" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781690</v>
+        <v>781705</v>
       </c>
       <c r="R61" t="n">
-        <v>7177998</v>
+        <v>7178041</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7087,13 +7087,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7112,41 +7116,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132115934</v>
+        <v>132115346</v>
       </c>
       <c r="B62" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7154,10 +7159,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>781602</v>
+        <v>781690</v>
       </c>
       <c r="R62" t="n">
-        <v>7178066</v>
+        <v>7177998</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7217,10 +7222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132116569</v>
+        <v>132115934</v>
       </c>
       <c r="B63" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7228,31 +7233,30 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7260,10 +7264,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>781705</v>
+        <v>781602</v>
       </c>
       <c r="R63" t="n">
-        <v>7178041</v>
+        <v>7178066</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7298,17 +7302,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132114700</v>
+        <v>132114993</v>
       </c>
       <c r="B66" t="n">
         <v>99098</v>
@@ -7585,10 +7585,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>781545</v>
+        <v>781633</v>
       </c>
       <c r="R66" t="n">
-        <v>7177946</v>
+        <v>7177971</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7648,7 +7648,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132114993</v>
+        <v>132114700</v>
       </c>
       <c r="B67" t="n">
         <v>99098</v>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>781633</v>
+        <v>781545</v>
       </c>
       <c r="R67" t="n">
-        <v>7177971</v>
+        <v>7177946</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7970,42 +7970,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132115576</v>
+        <v>132115737</v>
       </c>
       <c r="B70" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>781656</v>
+        <v>781633</v>
       </c>
       <c r="R70" t="n">
-        <v>7178009</v>
+        <v>7178011</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8051,17 +8051,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8080,7 +8076,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132116562</v>
+        <v>132115576</v>
       </c>
       <c r="B71" t="n">
         <v>57948</v>
@@ -8123,10 +8119,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>781688</v>
+        <v>781656</v>
       </c>
       <c r="R71" t="n">
-        <v>7178030</v>
+        <v>7178009</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8163,7 +8159,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>typiska barksprätt</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8190,10 +8186,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132115643</v>
+        <v>132116562</v>
       </c>
       <c r="B72" t="n">
-        <v>80422</v>
+        <v>57948</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8201,30 +8197,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8232,10 +8229,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>781644</v>
+        <v>781688</v>
       </c>
       <c r="R72" t="n">
-        <v>7178004</v>
+        <v>7178030</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8272,16 +8269,15 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>på en gammal sälg</t>
+          <t>typiska barksprätt</t>
         </is>
       </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8300,42 +8296,41 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132115737</v>
+        <v>132115643</v>
       </c>
       <c r="B73" t="n">
-        <v>99098</v>
+        <v>80422</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8343,10 +8338,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>781633</v>
+        <v>781644</v>
       </c>
       <c r="R73" t="n">
-        <v>7178011</v>
+        <v>7178004</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8379,6 +8374,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -2286,38 +2286,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132116069</v>
+        <v>132114839</v>
       </c>
       <c r="B17" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2325,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781642</v>
+        <v>781551</v>
       </c>
       <c r="R17" t="n">
-        <v>7178096</v>
+        <v>7177965</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,17 +2367,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2392,41 +2392,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132116152</v>
+        <v>132115248</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2434,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781634</v>
+        <v>781662</v>
       </c>
       <c r="R18" t="n">
-        <v>7178089</v>
+        <v>7177984</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,6 +2471,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,42 +2503,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132114839</v>
+        <v>132116069</v>
       </c>
       <c r="B19" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2540,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781551</v>
+        <v>781642</v>
       </c>
       <c r="R19" t="n">
-        <v>7177965</v>
+        <v>7178096</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,13 +2580,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2603,42 +2609,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132115248</v>
+        <v>132116152</v>
       </c>
       <c r="B20" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2646,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781662</v>
+        <v>781634</v>
       </c>
       <c r="R20" t="n">
-        <v>7177984</v>
+        <v>7178089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,11 +2687,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -4218,42 +4218,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132114726</v>
+        <v>132115061</v>
       </c>
       <c r="B35" t="n">
-        <v>99098</v>
+        <v>92191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4261,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781546</v>
+        <v>781656</v>
       </c>
       <c r="R35" t="n">
-        <v>7177958</v>
+        <v>7177972</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,6 +4296,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,7 +4328,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132116584</v>
+        <v>132114726</v>
       </c>
       <c r="B36" t="n">
         <v>99098</v>
@@ -4367,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781716</v>
+        <v>781546</v>
       </c>
       <c r="R36" t="n">
-        <v>7178070</v>
+        <v>7177958</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,7 +4434,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132115209</v>
+        <v>132116584</v>
       </c>
       <c r="B37" t="n">
         <v>99098</v>
@@ -4473,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>781663</v>
+        <v>781716</v>
       </c>
       <c r="R37" t="n">
-        <v>7177982</v>
+        <v>7178070</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4536,41 +4540,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132115061</v>
+        <v>132115209</v>
       </c>
       <c r="B38" t="n">
-        <v>92191</v>
+        <v>99098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4578,10 +4583,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>781656</v>
+        <v>781663</v>
       </c>
       <c r="R38" t="n">
-        <v>7177972</v>
+        <v>7177982</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,11 +4619,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,42 +4646,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132116829</v>
+        <v>132115870</v>
       </c>
       <c r="B39" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781713</v>
+        <v>781624</v>
       </c>
       <c r="R39" t="n">
-        <v>7178098</v>
+        <v>7178022</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,17 +4727,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4756,42 +4752,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132120397</v>
+        <v>132115918</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4799,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781702</v>
+        <v>781592</v>
       </c>
       <c r="R40" t="n">
-        <v>7178053</v>
+        <v>7178057</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4837,17 +4833,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4866,10 +4858,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132116218</v>
+        <v>132116829</v>
       </c>
       <c r="B41" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,16 +4869,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4909,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>781643</v>
+        <v>781713</v>
       </c>
       <c r="R41" t="n">
-        <v>7178078</v>
+        <v>7178098</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4949,14 +4941,14 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -4976,42 +4968,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132115870</v>
+        <v>132120397</v>
       </c>
       <c r="B42" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5019,10 +5011,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>781624</v>
+        <v>781702</v>
       </c>
       <c r="R42" t="n">
-        <v>7178022</v>
+        <v>7178053</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5057,13 +5049,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5082,42 +5078,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132115918</v>
+        <v>132116218</v>
       </c>
       <c r="B43" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5125,10 +5121,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>781592</v>
+        <v>781643</v>
       </c>
       <c r="R43" t="n">
-        <v>7178057</v>
+        <v>7178078</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,13 +5159,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132116569</v>
+        <v>132115934</v>
       </c>
       <c r="B61" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7017,31 +7017,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7049,10 +7048,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781705</v>
+        <v>781602</v>
       </c>
       <c r="R61" t="n">
-        <v>7178041</v>
+        <v>7178066</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7087,17 +7086,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7116,42 +7111,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132115346</v>
+        <v>132116569</v>
       </c>
       <c r="B62" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7159,10 +7154,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>781690</v>
+        <v>781705</v>
       </c>
       <c r="R62" t="n">
-        <v>7177998</v>
+        <v>7178041</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7197,13 +7192,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7222,41 +7221,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132115934</v>
+        <v>132115346</v>
       </c>
       <c r="B63" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>781602</v>
+        <v>781690</v>
       </c>
       <c r="R63" t="n">
-        <v>7178066</v>
+        <v>7177998</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7327,42 +7327,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132114698</v>
+        <v>132114993</v>
       </c>
       <c r="B64" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>781535</v>
+        <v>781633</v>
       </c>
       <c r="R64" t="n">
-        <v>7177946</v>
+        <v>7177971</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7408,17 +7408,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>bohål i tall</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7437,42 +7433,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132116691</v>
+        <v>132114700</v>
       </c>
       <c r="B65" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7480,10 +7476,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>781724</v>
+        <v>781545</v>
       </c>
       <c r="R65" t="n">
-        <v>7178057</v>
+        <v>7177946</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7524,6 +7520,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7542,42 +7539,42 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132114993</v>
+        <v>132114698</v>
       </c>
       <c r="B66" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7585,10 +7582,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>781633</v>
+        <v>781535</v>
       </c>
       <c r="R66" t="n">
-        <v>7177971</v>
+        <v>7177946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7623,13 +7620,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>bohål i tall</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7648,42 +7649,42 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132114700</v>
+        <v>132116691</v>
       </c>
       <c r="B67" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7691,10 +7692,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>781545</v>
+        <v>781724</v>
       </c>
       <c r="R67" t="n">
-        <v>7177946</v>
+        <v>7178057</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7735,7 +7736,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -4218,41 +4218,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132115061</v>
+        <v>132114726</v>
       </c>
       <c r="B35" t="n">
-        <v>92191</v>
+        <v>99098</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4260,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781656</v>
+        <v>781546</v>
       </c>
       <c r="R35" t="n">
-        <v>7177972</v>
+        <v>7177958</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4296,11 +4297,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4328,7 +4324,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132114726</v>
+        <v>132116584</v>
       </c>
       <c r="B36" t="n">
         <v>99098</v>
@@ -4371,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781546</v>
+        <v>781716</v>
       </c>
       <c r="R36" t="n">
-        <v>7177958</v>
+        <v>7178070</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4434,7 +4430,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132116584</v>
+        <v>132115209</v>
       </c>
       <c r="B37" t="n">
         <v>99098</v>
@@ -4477,10 +4473,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>781716</v>
+        <v>781663</v>
       </c>
       <c r="R37" t="n">
-        <v>7178070</v>
+        <v>7177982</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,42 +4536,41 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132115209</v>
+        <v>132115061</v>
       </c>
       <c r="B38" t="n">
-        <v>99098</v>
+        <v>92191</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4583,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>781663</v>
+        <v>781656</v>
       </c>
       <c r="R38" t="n">
-        <v>7177982</v>
+        <v>7177972</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4619,6 +4614,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,42 +4646,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132115870</v>
+        <v>132116829</v>
       </c>
       <c r="B39" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781624</v>
+        <v>781713</v>
       </c>
       <c r="R39" t="n">
-        <v>7178022</v>
+        <v>7178098</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,13 +4727,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4752,42 +4756,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132115918</v>
+        <v>132120397</v>
       </c>
       <c r="B40" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4795,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781592</v>
+        <v>781702</v>
       </c>
       <c r="R40" t="n">
-        <v>7178057</v>
+        <v>7178053</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4833,13 +4837,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4858,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132116829</v>
+        <v>132116218</v>
       </c>
       <c r="B41" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4869,16 +4877,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4901,10 +4909,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>781713</v>
+        <v>781643</v>
       </c>
       <c r="R41" t="n">
-        <v>7178098</v>
+        <v>7178078</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4941,14 +4949,14 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -4968,42 +4976,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132120397</v>
+        <v>132115870</v>
       </c>
       <c r="B42" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5011,10 +5019,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>781702</v>
+        <v>781624</v>
       </c>
       <c r="R42" t="n">
-        <v>7178053</v>
+        <v>7178022</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,17 +5057,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5078,42 +5082,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132116218</v>
+        <v>132115918</v>
       </c>
       <c r="B43" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5121,10 +5125,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>781643</v>
+        <v>781592</v>
       </c>
       <c r="R43" t="n">
-        <v>7178078</v>
+        <v>7178057</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,17 +5163,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6043,41 +6043,42 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132115443</v>
+        <v>132114938</v>
       </c>
       <c r="B52" t="n">
-        <v>79317</v>
+        <v>99098</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6085,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>781657</v>
+        <v>781627</v>
       </c>
       <c r="R52" t="n">
-        <v>7178001</v>
+        <v>7177962</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6148,10 +6149,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132116712</v>
+        <v>132115443</v>
       </c>
       <c r="B53" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6159,31 +6160,30 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>781744</v>
+        <v>781657</v>
       </c>
       <c r="R53" t="n">
-        <v>7178073</v>
+        <v>7178001</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6229,17 +6229,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6258,7 +6254,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132114931</v>
+        <v>132116712</v>
       </c>
       <c r="B54" t="n">
         <v>57945</v>
@@ -6291,7 +6287,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6301,10 +6297,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>781630</v>
+        <v>781744</v>
       </c>
       <c r="R54" t="n">
-        <v>7177957</v>
+        <v>7178073</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6341,7 +6337,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>hack i två lågor</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6368,42 +6364,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132114938</v>
+        <v>132114931</v>
       </c>
       <c r="B55" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6411,10 +6407,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>781627</v>
+        <v>781630</v>
       </c>
       <c r="R55" t="n">
-        <v>7177962</v>
+        <v>7177957</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6449,13 +6445,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>hack i två lågor</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7327,42 +7327,42 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132114993</v>
+        <v>132114698</v>
       </c>
       <c r="B64" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>781633</v>
+        <v>781535</v>
       </c>
       <c r="R64" t="n">
-        <v>7177971</v>
+        <v>7177946</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7408,13 +7408,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>bohål i tall</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7433,42 +7437,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132114700</v>
+        <v>132116691</v>
       </c>
       <c r="B65" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7476,10 +7480,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>781545</v>
+        <v>781724</v>
       </c>
       <c r="R65" t="n">
-        <v>7177946</v>
+        <v>7178057</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7520,7 +7524,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7539,42 +7542,42 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132114698</v>
+        <v>132114993</v>
       </c>
       <c r="B66" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7582,10 +7585,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>781535</v>
+        <v>781633</v>
       </c>
       <c r="R66" t="n">
-        <v>7177946</v>
+        <v>7177971</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7620,17 +7623,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>bohål i tall</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7649,42 +7648,42 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132116691</v>
+        <v>132114700</v>
       </c>
       <c r="B67" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7692,10 +7691,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>781724</v>
+        <v>781545</v>
       </c>
       <c r="R67" t="n">
-        <v>7178057</v>
+        <v>7177946</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7736,6 +7735,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132116162</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132116033</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>132115035</v>
       </c>
       <c r="B5" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>132117131</v>
       </c>
       <c r="B6" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>132115952</v>
       </c>
       <c r="B7" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>132115712</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>132114881</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,41 +1537,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132115561</v>
+        <v>132116022</v>
       </c>
       <c r="B10" t="n">
-        <v>91892</v>
+        <v>99106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1579,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781653</v>
+        <v>781624</v>
       </c>
       <c r="R10" t="n">
-        <v>7178001</v>
+        <v>7178093</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132116022</v>
+        <v>132115520</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781624</v>
+        <v>781655</v>
       </c>
       <c r="R11" t="n">
-        <v>7178093</v>
+        <v>7178001</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,6 +1722,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,42 +1754,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132115520</v>
+        <v>132115561</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>91898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,7 +1796,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781655</v>
+        <v>781653</v>
       </c>
       <c r="R12" t="n">
         <v>7178001</v>
@@ -1827,11 +1832,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,42 +1859,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132116915</v>
+        <v>132115009</v>
       </c>
       <c r="B13" t="n">
-        <v>57945</v>
+        <v>80453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1902,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781709</v>
+        <v>781643</v>
       </c>
       <c r="R13" t="n">
-        <v>7178098</v>
+        <v>7177977</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1937,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>färska typiska hack i gran</t>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,6 +1946,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132115729</v>
+        <v>132116915</v>
       </c>
       <c r="B14" t="n">
-        <v>83163</v>
+        <v>57946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,30 +1976,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2011,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781627</v>
+        <v>781709</v>
       </c>
       <c r="R14" t="n">
-        <v>7178004</v>
+        <v>7178098</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,13 +2046,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska typiska hack i gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2074,36 +2075,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132115009</v>
+        <v>132115729</v>
       </c>
       <c r="B15" t="n">
-        <v>80451</v>
+        <v>83165</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2112,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781643</v>
+        <v>781627</v>
       </c>
       <c r="R15" t="n">
-        <v>7177977</v>
+        <v>7178004</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,11 +2153,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,7 +2183,7 @@
         <v>132116228</v>
       </c>
       <c r="B16" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,42 +2286,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132114839</v>
+        <v>132116152</v>
       </c>
       <c r="B17" t="n">
-        <v>99098</v>
+        <v>79319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781551</v>
+        <v>781634</v>
       </c>
       <c r="R17" t="n">
-        <v>7177965</v>
+        <v>7178089</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132115248</v>
+        <v>132114839</v>
       </c>
       <c r="B18" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2435,10 +2434,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781662</v>
+        <v>781551</v>
       </c>
       <c r="R18" t="n">
-        <v>7177984</v>
+        <v>7177965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2471,11 +2470,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,38 +2497,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132116069</v>
+        <v>132115248</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2542,10 +2540,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781642</v>
+        <v>781662</v>
       </c>
       <c r="R19" t="n">
-        <v>7178096</v>
+        <v>7177984</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,15 +2580,16 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2609,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132116152</v>
+        <v>132116069</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,30 +2619,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2651,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781634</v>
+        <v>781642</v>
       </c>
       <c r="R20" t="n">
-        <v>7178089</v>
+        <v>7178096</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,13 +2685,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2714,42 +2714,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132116701</v>
+        <v>132115308</v>
       </c>
       <c r="B21" t="n">
-        <v>99098</v>
+        <v>92086</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1588</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2757,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781744</v>
+        <v>781683</v>
       </c>
       <c r="R21" t="n">
-        <v>7178071</v>
+        <v>7177990</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,42 +2819,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132115101</v>
+        <v>132117060</v>
       </c>
       <c r="B22" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2863,10 +2862,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781657</v>
+        <v>781577</v>
       </c>
       <c r="R22" t="n">
-        <v>7177964</v>
+        <v>7178033</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,16 +2902,15 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>rikligt uppe på ett litet stenblock</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2931,42 +2929,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132114890</v>
+        <v>132116478</v>
       </c>
       <c r="B23" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2974,10 +2972,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781609</v>
+        <v>781686</v>
       </c>
       <c r="R23" t="n">
-        <v>7177971</v>
+        <v>7178038</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,13 +3010,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>födosökande i granar</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3037,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132115704</v>
+        <v>132116701</v>
       </c>
       <c r="B24" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781632</v>
+        <v>781744</v>
       </c>
       <c r="R24" t="n">
-        <v>7178004</v>
+        <v>7178071</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,10 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132116490</v>
+        <v>132115101</v>
       </c>
       <c r="B25" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,10 +3188,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781684</v>
+        <v>781657</v>
       </c>
       <c r="R25" t="n">
-        <v>7178030</v>
+        <v>7177964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,6 +3224,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>rikligt uppe på ett litet stenblock</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3249,41 +3256,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132115308</v>
+        <v>132114890</v>
       </c>
       <c r="B26" t="n">
-        <v>92080</v>
+        <v>99106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3291,10 +3299,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781683</v>
+        <v>781609</v>
       </c>
       <c r="R26" t="n">
-        <v>7177990</v>
+        <v>7177971</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,42 +3362,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132117060</v>
+        <v>132115704</v>
       </c>
       <c r="B27" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3397,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781577</v>
+        <v>781632</v>
       </c>
       <c r="R27" t="n">
-        <v>7178033</v>
+        <v>7178004</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3435,17 +3443,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3464,42 +3468,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132116478</v>
+        <v>132116490</v>
       </c>
       <c r="B28" t="n">
-        <v>57948</v>
+        <v>99106</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3507,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781686</v>
+        <v>781684</v>
       </c>
       <c r="R28" t="n">
-        <v>7178038</v>
+        <v>7178030</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3545,17 +3549,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>födosökande i granar</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>132115227</v>
       </c>
       <c r="B29" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>132115000</v>
       </c>
       <c r="B30" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>132114873</v>
       </c>
       <c r="B31" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3891,42 +3891,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132115082</v>
+        <v>132116734</v>
       </c>
       <c r="B32" t="n">
-        <v>99098</v>
+        <v>57946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>781661</v>
+        <v>781737</v>
       </c>
       <c r="R32" t="n">
-        <v>7177969</v>
+        <v>7178076</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3972,13 +3972,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3997,10 +4001,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132114818</v>
+        <v>132115082</v>
       </c>
       <c r="B33" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4040,10 +4044,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>781549</v>
+        <v>781661</v>
       </c>
       <c r="R33" t="n">
-        <v>7177957</v>
+        <v>7177969</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,11 +4080,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4108,42 +4107,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132116734</v>
+        <v>132114818</v>
       </c>
       <c r="B34" t="n">
-        <v>57945</v>
+        <v>99106</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4151,10 +4150,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781737</v>
+        <v>781549</v>
       </c>
       <c r="R34" t="n">
-        <v>7178076</v>
+        <v>7177957</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4191,7 +4190,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4200,6 +4199,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4218,42 +4218,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132114726</v>
+        <v>132115061</v>
       </c>
       <c r="B35" t="n">
-        <v>99098</v>
+        <v>92197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4261,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781546</v>
+        <v>781656</v>
       </c>
       <c r="R35" t="n">
-        <v>7177958</v>
+        <v>7177972</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4297,6 +4296,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4324,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132116584</v>
+        <v>132114726</v>
       </c>
       <c r="B36" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781716</v>
+        <v>781546</v>
       </c>
       <c r="R36" t="n">
-        <v>7178070</v>
+        <v>7177958</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4430,10 +4434,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132115209</v>
+        <v>132116584</v>
       </c>
       <c r="B37" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4473,10 +4477,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>781663</v>
+        <v>781716</v>
       </c>
       <c r="R37" t="n">
-        <v>7177982</v>
+        <v>7178070</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4536,41 +4540,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132115061</v>
+        <v>132115209</v>
       </c>
       <c r="B38" t="n">
-        <v>92191</v>
+        <v>99106</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4578,10 +4583,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>781656</v>
+        <v>781663</v>
       </c>
       <c r="R38" t="n">
-        <v>7177972</v>
+        <v>7177982</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4614,11 +4619,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,10 +4646,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132116829</v>
+        <v>132116218</v>
       </c>
       <c r="B39" t="n">
-        <v>57948</v>
+        <v>57946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4657,16 +4657,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781713</v>
+        <v>781643</v>
       </c>
       <c r="R39" t="n">
-        <v>7178098</v>
+        <v>7178078</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,14 +4729,14 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
@@ -4756,10 +4756,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132120397</v>
+        <v>132116829</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781702</v>
+        <v>781713</v>
       </c>
       <c r="R40" t="n">
-        <v>7178053</v>
+        <v>7178098</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4866,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132116218</v>
+        <v>132120397</v>
       </c>
       <c r="B41" t="n">
-        <v>57945</v>
+        <v>57949</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,16 +4877,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>781643</v>
+        <v>781702</v>
       </c>
       <c r="R41" t="n">
-        <v>7178078</v>
+        <v>7178053</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4949,14 +4949,14 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -4979,7 +4979,7 @@
         <v>132115870</v>
       </c>
       <c r="B42" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>132115918</v>
       </c>
       <c r="B43" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5188,42 +5188,41 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132116006</v>
+        <v>132116288</v>
       </c>
       <c r="B44" t="n">
-        <v>99098</v>
+        <v>91898</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5231,10 +5230,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>781602</v>
+        <v>781649</v>
       </c>
       <c r="R44" t="n">
-        <v>7178094</v>
+        <v>7178072</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5294,10 +5293,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132115899</v>
+        <v>132116006</v>
       </c>
       <c r="B45" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5337,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>781608</v>
+        <v>781602</v>
       </c>
       <c r="R45" t="n">
-        <v>7178045</v>
+        <v>7178094</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,10 +5399,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132115962</v>
+        <v>132115899</v>
       </c>
       <c r="B46" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5443,10 +5442,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>781591</v>
+        <v>781608</v>
       </c>
       <c r="R46" t="n">
-        <v>7178081</v>
+        <v>7178045</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5506,41 +5505,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132116288</v>
+        <v>132115962</v>
       </c>
       <c r="B47" t="n">
-        <v>91892</v>
+        <v>99106</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>781649</v>
+        <v>781591</v>
       </c>
       <c r="R47" t="n">
-        <v>7178072</v>
+        <v>7178081</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5614,7 +5614,7 @@
         <v>132116133</v>
       </c>
       <c r="B48" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>132116371</v>
       </c>
       <c r="B49" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>132115856</v>
       </c>
       <c r="B50" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>132115808</v>
       </c>
       <c r="B51" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>132114938</v>
       </c>
       <c r="B52" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6149,10 +6149,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132115443</v>
+        <v>132116712</v>
       </c>
       <c r="B53" t="n">
-        <v>79317</v>
+        <v>57946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6160,30 +6160,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6191,10 +6192,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>781657</v>
+        <v>781744</v>
       </c>
       <c r="R53" t="n">
-        <v>7178001</v>
+        <v>7178073</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6229,13 +6230,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6254,10 +6259,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132116712</v>
+        <v>132114931</v>
       </c>
       <c r="B54" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6287,7 +6292,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6297,10 +6302,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>781744</v>
+        <v>781630</v>
       </c>
       <c r="R54" t="n">
-        <v>7178073</v>
+        <v>7177957</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6337,7 +6342,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>hack i två lågor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6364,10 +6369,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132114931</v>
+        <v>132115443</v>
       </c>
       <c r="B55" t="n">
-        <v>57945</v>
+        <v>79319</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6375,31 +6380,30 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6407,10 +6411,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>781630</v>
+        <v>781657</v>
       </c>
       <c r="R55" t="n">
-        <v>7177957</v>
+        <v>7178001</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6445,17 +6449,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>hack i två lågor</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6474,10 +6474,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132117193</v>
+        <v>132117003</v>
       </c>
       <c r="B56" t="n">
-        <v>57948</v>
+        <v>91898</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6485,27 +6485,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6513,7 +6516,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>781651</v>
+        <v>781692</v>
       </c>
       <c r="R56" t="n">
         <v>7178085</v>
@@ -6551,17 +6554,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6580,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132117003</v>
+        <v>132115371</v>
       </c>
       <c r="B57" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6622,10 +6621,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>781692</v>
+        <v>781688</v>
       </c>
       <c r="R57" t="n">
-        <v>7178085</v>
+        <v>7178003</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6685,10 +6684,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132115371</v>
+        <v>132117193</v>
       </c>
       <c r="B58" t="n">
-        <v>91892</v>
+        <v>57949</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6696,30 +6695,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6727,10 +6723,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>781688</v>
+        <v>781651</v>
       </c>
       <c r="R58" t="n">
-        <v>7178003</v>
+        <v>7178085</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,13 +6761,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6790,42 +6790,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132114915</v>
+        <v>132116952</v>
       </c>
       <c r="B59" t="n">
-        <v>57945</v>
+        <v>99106</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>781609</v>
+        <v>781696</v>
       </c>
       <c r="R59" t="n">
-        <v>7177970</v>
+        <v>7178090</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,17 +6871,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>stort bohål i ihålig gammal asp</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6900,42 +6896,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132116952</v>
+        <v>132114915</v>
       </c>
       <c r="B60" t="n">
-        <v>99098</v>
+        <v>57946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6943,10 +6939,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>781696</v>
+        <v>781609</v>
       </c>
       <c r="R60" t="n">
-        <v>7178090</v>
+        <v>7177970</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6981,13 +6977,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>stort bohål i ihålig gammal asp</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132115934</v>
+        <v>132116569</v>
       </c>
       <c r="B61" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7017,30 +7017,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7048,10 +7049,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781602</v>
+        <v>781705</v>
       </c>
       <c r="R61" t="n">
-        <v>7178066</v>
+        <v>7178041</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7086,13 +7087,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7111,10 +7116,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132116569</v>
+        <v>132115934</v>
       </c>
       <c r="B62" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7122,31 +7127,30 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7154,10 +7158,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>781705</v>
+        <v>781602</v>
       </c>
       <c r="R62" t="n">
-        <v>7178041</v>
+        <v>7178066</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7192,17 +7196,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v>132115346</v>
       </c>
       <c r="B63" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>132114698</v>
       </c>
       <c r="B64" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>132116691</v>
       </c>
       <c r="B65" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>132114993</v>
       </c>
       <c r="B66" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>132114700</v>
       </c>
       <c r="B67" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>132116300</v>
       </c>
       <c r="B68" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>132116723</v>
       </c>
       <c r="B69" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7970,42 +7970,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132115737</v>
+        <v>132115576</v>
       </c>
       <c r="B70" t="n">
-        <v>99098</v>
+        <v>57949</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>781633</v>
+        <v>781656</v>
       </c>
       <c r="R70" t="n">
-        <v>7178011</v>
+        <v>7178009</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8051,13 +8051,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8076,10 +8080,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132115576</v>
+        <v>132116562</v>
       </c>
       <c r="B71" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8119,10 +8123,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>781656</v>
+        <v>781688</v>
       </c>
       <c r="R71" t="n">
-        <v>7178009</v>
+        <v>7178030</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8159,7 +8163,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>typiska barksprätt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8186,10 +8190,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132116562</v>
+        <v>132115643</v>
       </c>
       <c r="B72" t="n">
-        <v>57948</v>
+        <v>80424</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8197,31 +8201,30 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8229,10 +8232,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>781688</v>
+        <v>781644</v>
       </c>
       <c r="R72" t="n">
-        <v>7178030</v>
+        <v>7178004</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8269,15 +8272,16 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>typiska barksprätt</t>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8296,41 +8300,42 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132115643</v>
+        <v>132115737</v>
       </c>
       <c r="B73" t="n">
-        <v>80422</v>
+        <v>99106</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8338,10 +8343,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>781644</v>
+        <v>781633</v>
       </c>
       <c r="R73" t="n">
-        <v>7178004</v>
+        <v>7178011</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8374,11 +8379,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -3786,41 +3786,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132114873</v>
+        <v>132115082</v>
       </c>
       <c r="B31" t="n">
-        <v>91898</v>
+        <v>99106</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3828,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781574</v>
+        <v>781661</v>
       </c>
       <c r="R31" t="n">
-        <v>7177976</v>
+        <v>7177969</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3891,42 +3892,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132116734</v>
+        <v>132114818</v>
       </c>
       <c r="B32" t="n">
-        <v>57946</v>
+        <v>99106</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3934,10 +3935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>781737</v>
+        <v>781549</v>
       </c>
       <c r="R32" t="n">
-        <v>7178076</v>
+        <v>7177957</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3974,7 +3975,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3983,6 +3984,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4001,42 +4003,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132115082</v>
+        <v>132114873</v>
       </c>
       <c r="B33" t="n">
-        <v>99106</v>
+        <v>91898</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4044,10 +4045,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>781661</v>
+        <v>781574</v>
       </c>
       <c r="R33" t="n">
-        <v>7177969</v>
+        <v>7177976</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4107,42 +4108,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132114818</v>
+        <v>132116734</v>
       </c>
       <c r="B34" t="n">
-        <v>99106</v>
+        <v>57946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4150,10 +4151,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781549</v>
+        <v>781737</v>
       </c>
       <c r="R34" t="n">
-        <v>7177957</v>
+        <v>7178076</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,7 +4191,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4199,7 +4200,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -6684,10 +6684,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132117193</v>
+        <v>132114915</v>
       </c>
       <c r="B58" t="n">
-        <v>57949</v>
+        <v>57946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6695,16 +6695,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6715,7 +6715,11 @@
       <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6723,10 +6727,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>781651</v>
+        <v>781609</v>
       </c>
       <c r="R58" t="n">
-        <v>7178085</v>
+        <v>7177970</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6763,14 +6767,14 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>stort bohål i ihålig gammal asp</t>
         </is>
       </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="b">
         <v>0</v>
@@ -6896,10 +6900,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132114915</v>
+        <v>132117193</v>
       </c>
       <c r="B60" t="n">
-        <v>57946</v>
+        <v>57949</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6907,16 +6911,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6927,11 +6931,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>781609</v>
+        <v>781651</v>
       </c>
       <c r="R60" t="n">
-        <v>7177970</v>
+        <v>7178085</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6979,14 +6979,14 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>stort bohål i ihålig gammal asp</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG60" t="b">
         <v>0</v>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132115576</v>
+        <v>132115643</v>
       </c>
       <c r="B70" t="n">
-        <v>57949</v>
+        <v>80424</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7981,31 +7981,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8013,10 +8012,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>781656</v>
+        <v>781644</v>
       </c>
       <c r="R70" t="n">
-        <v>7178009</v>
+        <v>7178004</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8053,15 +8052,16 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8080,7 +8080,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132116562</v>
+        <v>132115576</v>
       </c>
       <c r="B71" t="n">
         <v>57949</v>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>781688</v>
+        <v>781656</v>
       </c>
       <c r="R71" t="n">
-        <v>7178030</v>
+        <v>7178009</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>typiska barksprätt</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8190,10 +8190,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132115643</v>
+        <v>132116562</v>
       </c>
       <c r="B72" t="n">
-        <v>80424</v>
+        <v>57949</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8201,30 +8201,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8232,10 +8233,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>781644</v>
+        <v>781688</v>
       </c>
       <c r="R72" t="n">
-        <v>7178004</v>
+        <v>7178030</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8272,16 +8273,15 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>på en gammal sälg</t>
+          <t>typiska barksprätt</t>
         </is>
       </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG72" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -675,42 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132116162</v>
+        <v>132120235</v>
       </c>
       <c r="B2" t="n">
-        <v>99106</v>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781632</v>
+        <v>781536</v>
       </c>
       <c r="R2" t="n">
-        <v>7178081</v>
+        <v>7177982</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>typiska gnagspår på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132116033</v>
+        <v>132116162</v>
       </c>
       <c r="B3" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781633</v>
+        <v>781632</v>
       </c>
       <c r="R3" t="n">
-        <v>7178101</v>
+        <v>7178081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,43 +893,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132120235</v>
+        <v>132116033</v>
       </c>
       <c r="B4" t="n">
-        <v>5179</v>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781536</v>
+        <v>781633</v>
       </c>
       <c r="R4" t="n">
-        <v>7177982</v>
+        <v>7178101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>typiska gnagspår på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>132115035</v>
       </c>
       <c r="B5" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132117131</v>
+        <v>132115712</v>
       </c>
       <c r="B6" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781577</v>
+        <v>781622</v>
       </c>
       <c r="R6" t="n">
-        <v>7178033</v>
+        <v>7178004</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
         <v>132115952</v>
       </c>
       <c r="B7" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132115712</v>
+        <v>132117131</v>
       </c>
       <c r="B8" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781622</v>
+        <v>781577</v>
       </c>
       <c r="R8" t="n">
-        <v>7178004</v>
+        <v>7178033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
         <v>132114881</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132116022</v>
+        <v>132115520</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781624</v>
+        <v>781655</v>
       </c>
       <c r="R10" t="n">
-        <v>7178093</v>
+        <v>7178001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1616,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,42 +1648,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132115520</v>
+        <v>132115561</v>
       </c>
       <c r="B11" t="n">
-        <v>99106</v>
+        <v>91908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1686,7 +1690,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781655</v>
+        <v>781653</v>
       </c>
       <c r="R11" t="n">
         <v>7178001</v>
@@ -1722,11 +1726,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,41 +1753,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132115561</v>
+        <v>132116022</v>
       </c>
       <c r="B12" t="n">
-        <v>91898</v>
+        <v>99116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781653</v>
+        <v>781624</v>
       </c>
       <c r="R12" t="n">
-        <v>7178001</v>
+        <v>7178093</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,36 +1859,40 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132115009</v>
+        <v>132115729</v>
       </c>
       <c r="B13" t="n">
-        <v>80453</v>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1897,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781643</v>
+        <v>781627</v>
       </c>
       <c r="R13" t="n">
-        <v>7177977</v>
+        <v>7178004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,11 +1937,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,42 +1964,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132116915</v>
+        <v>132116228</v>
       </c>
       <c r="B14" t="n">
-        <v>57946</v>
+        <v>99116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2008,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781709</v>
+        <v>781649</v>
       </c>
       <c r="R14" t="n">
-        <v>7178098</v>
+        <v>7178072</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,17 +2045,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska typiska hack i gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2075,40 +2070,36 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132115729</v>
+        <v>132115009</v>
       </c>
       <c r="B15" t="n">
-        <v>83165</v>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2117,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781627</v>
+        <v>781643</v>
       </c>
       <c r="R15" t="n">
-        <v>7178004</v>
+        <v>7177977</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,6 +2144,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2180,42 +2176,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132116228</v>
+        <v>132116915</v>
       </c>
       <c r="B16" t="n">
-        <v>99106</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2223,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781649</v>
+        <v>781709</v>
       </c>
       <c r="R16" t="n">
-        <v>7178072</v>
+        <v>7178098</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,13 +2257,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färska typiska hack i gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,41 +2286,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132116152</v>
+        <v>132115248</v>
       </c>
       <c r="B17" t="n">
-        <v>79319</v>
+        <v>99116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2328,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781634</v>
+        <v>781662</v>
       </c>
       <c r="R17" t="n">
-        <v>7178089</v>
+        <v>7177984</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2364,6 +2365,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2394,7 +2400,7 @@
         <v>132114839</v>
       </c>
       <c r="B18" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,42 +2503,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132115248</v>
+        <v>132116152</v>
       </c>
       <c r="B19" t="n">
-        <v>99106</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2540,10 +2545,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781662</v>
+        <v>781634</v>
       </c>
       <c r="R19" t="n">
-        <v>7177984</v>
+        <v>7178089</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,11 +2581,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2611,7 +2611,7 @@
         <v>132116069</v>
       </c>
       <c r="B20" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>132115308</v>
       </c>
       <c r="B21" t="n">
-        <v>92086</v>
+        <v>92096</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>132117060</v>
       </c>
       <c r="B22" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>132116478</v>
       </c>
       <c r="B23" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>132116701</v>
       </c>
       <c r="B24" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132115101</v>
+        <v>132115704</v>
       </c>
       <c r="B25" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781657</v>
+        <v>781632</v>
       </c>
       <c r="R25" t="n">
-        <v>7177964</v>
+        <v>7178004</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,11 +3224,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>rikligt uppe på ett litet stenblock</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3259,7 +3254,7 @@
         <v>132114890</v>
       </c>
       <c r="B26" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,10 +3357,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132115704</v>
+        <v>132116490</v>
       </c>
       <c r="B27" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3405,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781632</v>
+        <v>781684</v>
       </c>
       <c r="R27" t="n">
-        <v>7178004</v>
+        <v>7178030</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,10 +3463,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132116490</v>
+        <v>132115101</v>
       </c>
       <c r="B28" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,10 +3506,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781684</v>
+        <v>781657</v>
       </c>
       <c r="R28" t="n">
-        <v>7178030</v>
+        <v>7177964</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3547,6 +3542,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>rikligt uppe på ett litet stenblock</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,7 +3577,7 @@
         <v>132115227</v>
       </c>
       <c r="B29" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>132115000</v>
       </c>
       <c r="B30" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3786,42 +3786,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132115082</v>
+        <v>132116734</v>
       </c>
       <c r="B31" t="n">
-        <v>99106</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781661</v>
+        <v>781737</v>
       </c>
       <c r="R31" t="n">
-        <v>7177969</v>
+        <v>7178076</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,13 +3867,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3895,7 +3899,7 @@
         <v>132114818</v>
       </c>
       <c r="B32" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4003,41 +4007,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132114873</v>
+        <v>132115082</v>
       </c>
       <c r="B33" t="n">
-        <v>91898</v>
+        <v>99116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4045,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>781574</v>
+        <v>781661</v>
       </c>
       <c r="R33" t="n">
-        <v>7177976</v>
+        <v>7177969</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4108,10 +4113,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132116734</v>
+        <v>132114873</v>
       </c>
       <c r="B34" t="n">
-        <v>57946</v>
+        <v>91908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4119,31 +4124,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4151,10 +4155,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781737</v>
+        <v>781574</v>
       </c>
       <c r="R34" t="n">
-        <v>7178076</v>
+        <v>7177976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,17 +4193,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>132115061</v>
       </c>
       <c r="B35" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132114726</v>
+        <v>132115209</v>
       </c>
       <c r="B36" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781546</v>
+        <v>781663</v>
       </c>
       <c r="R36" t="n">
-        <v>7177958</v>
+        <v>7177982</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
         <v>132116584</v>
       </c>
       <c r="B37" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4540,10 +4540,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132115209</v>
+        <v>132114726</v>
       </c>
       <c r="B38" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>781663</v>
+        <v>781546</v>
       </c>
       <c r="R38" t="n">
-        <v>7177982</v>
+        <v>7177958</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4646,42 +4646,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132116218</v>
+        <v>132115870</v>
       </c>
       <c r="B39" t="n">
-        <v>57946</v>
+        <v>99116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781643</v>
+        <v>781624</v>
       </c>
       <c r="R39" t="n">
-        <v>7178078</v>
+        <v>7178022</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,17 +4727,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4756,42 +4752,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132116829</v>
+        <v>132115918</v>
       </c>
       <c r="B40" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4799,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781713</v>
+        <v>781592</v>
       </c>
       <c r="R40" t="n">
-        <v>7178098</v>
+        <v>7178057</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4837,17 +4833,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4866,10 +4858,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132120397</v>
+        <v>132116218</v>
       </c>
       <c r="B41" t="n">
-        <v>57949</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,16 +4869,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4909,10 +4901,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>781702</v>
+        <v>781643</v>
       </c>
       <c r="R41" t="n">
-        <v>7178053</v>
+        <v>7178078</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4949,14 +4941,14 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -4976,42 +4968,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132115870</v>
+        <v>132116829</v>
       </c>
       <c r="B42" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5019,10 +5011,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>781624</v>
+        <v>781713</v>
       </c>
       <c r="R42" t="n">
-        <v>7178022</v>
+        <v>7178098</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5057,13 +5049,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5082,42 +5078,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132115918</v>
+        <v>132120397</v>
       </c>
       <c r="B43" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5125,10 +5121,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>781592</v>
+        <v>781702</v>
       </c>
       <c r="R43" t="n">
-        <v>7178057</v>
+        <v>7178053</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,13 +5159,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>132116288</v>
       </c>
       <c r="B44" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132116006</v>
+        <v>132115962</v>
       </c>
       <c r="B45" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>781602</v>
+        <v>781591</v>
       </c>
       <c r="R45" t="n">
-        <v>7178094</v>
+        <v>7178081</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,10 +5399,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132115899</v>
+        <v>132116006</v>
       </c>
       <c r="B46" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>781608</v>
+        <v>781602</v>
       </c>
       <c r="R46" t="n">
-        <v>7178045</v>
+        <v>7178094</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132115962</v>
+        <v>132115899</v>
       </c>
       <c r="B47" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>781591</v>
+        <v>781608</v>
       </c>
       <c r="R47" t="n">
-        <v>7178081</v>
+        <v>7178045</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5611,42 +5611,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132116133</v>
+        <v>132115856</v>
       </c>
       <c r="B48" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>781637</v>
+        <v>781632</v>
       </c>
       <c r="R48" t="n">
-        <v>7178091</v>
+        <v>7178016</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5692,17 +5692,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>observerad på nära håll vid födosök</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5721,42 +5717,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132116371</v>
+        <v>132115808</v>
       </c>
       <c r="B49" t="n">
-        <v>57949</v>
+        <v>99116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5764,10 +5760,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>781671</v>
+        <v>781627</v>
       </c>
       <c r="R49" t="n">
-        <v>7178082</v>
+        <v>7178015</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5802,17 +5798,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>födosökande, observerad på ca 5 meters håll</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5831,42 +5823,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132115856</v>
+        <v>132116133</v>
       </c>
       <c r="B50" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5874,10 +5866,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>781632</v>
+        <v>781637</v>
       </c>
       <c r="R50" t="n">
-        <v>7178016</v>
+        <v>7178091</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5912,13 +5904,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>observerad på nära håll vid födosök</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5937,42 +5933,42 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132115808</v>
+        <v>132116371</v>
       </c>
       <c r="B51" t="n">
-        <v>99106</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5980,10 +5976,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>781627</v>
+        <v>781671</v>
       </c>
       <c r="R51" t="n">
-        <v>7178015</v>
+        <v>7178082</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6018,13 +6014,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>födosökande, observerad på ca 5 meters håll</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>132114938</v>
       </c>
       <c r="B52" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6149,10 +6149,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132116712</v>
+        <v>132115443</v>
       </c>
       <c r="B53" t="n">
-        <v>57946</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6160,31 +6160,30 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6192,10 +6191,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>781744</v>
+        <v>781657</v>
       </c>
       <c r="R53" t="n">
-        <v>7178073</v>
+        <v>7178001</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6230,17 +6229,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6259,10 +6254,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132114931</v>
+        <v>132116712</v>
       </c>
       <c r="B54" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6292,7 +6287,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6302,10 +6297,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>781630</v>
+        <v>781744</v>
       </c>
       <c r="R54" t="n">
-        <v>7177957</v>
+        <v>7178073</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6342,7 +6337,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>hack i två lågor</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6369,10 +6364,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132115443</v>
+        <v>132114931</v>
       </c>
       <c r="B55" t="n">
-        <v>79319</v>
+        <v>57950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6380,30 +6375,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6411,10 +6407,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>781657</v>
+        <v>781630</v>
       </c>
       <c r="R55" t="n">
-        <v>7178001</v>
+        <v>7177957</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6449,13 +6445,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>hack i två lågor</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6474,10 +6474,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132117003</v>
+        <v>132117193</v>
       </c>
       <c r="B56" t="n">
-        <v>91898</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6485,30 +6485,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6516,7 +6513,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>781692</v>
+        <v>781651</v>
       </c>
       <c r="R56" t="n">
         <v>7178085</v>
@@ -6554,13 +6551,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6579,41 +6580,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132115371</v>
+        <v>132116952</v>
       </c>
       <c r="B57" t="n">
-        <v>91898</v>
+        <v>99116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6621,10 +6623,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>781688</v>
+        <v>781696</v>
       </c>
       <c r="R57" t="n">
-        <v>7178003</v>
+        <v>7178090</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6687,7 +6689,7 @@
         <v>132114915</v>
       </c>
       <c r="B58" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6794,42 +6796,41 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132116952</v>
+        <v>132117003</v>
       </c>
       <c r="B59" t="n">
-        <v>99106</v>
+        <v>91908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6837,10 +6838,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>781696</v>
+        <v>781692</v>
       </c>
       <c r="R59" t="n">
-        <v>7178090</v>
+        <v>7178085</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6900,10 +6901,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132117193</v>
+        <v>132115371</v>
       </c>
       <c r="B60" t="n">
-        <v>57949</v>
+        <v>91908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6911,27 +6912,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6939,10 +6943,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>781651</v>
+        <v>781688</v>
       </c>
       <c r="R60" t="n">
-        <v>7178085</v>
+        <v>7178003</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,17 +6981,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132116569</v>
+        <v>132115934</v>
       </c>
       <c r="B61" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7017,31 +7017,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7049,10 +7048,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781705</v>
+        <v>781602</v>
       </c>
       <c r="R61" t="n">
-        <v>7178041</v>
+        <v>7178066</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7087,17 +7086,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7116,10 +7111,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132115934</v>
+        <v>132116569</v>
       </c>
       <c r="B62" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7127,30 +7122,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7158,10 +7154,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>781602</v>
+        <v>781705</v>
       </c>
       <c r="R62" t="n">
-        <v>7178066</v>
+        <v>7178041</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7196,13 +7192,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v>132115346</v>
       </c>
       <c r="B63" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>132114698</v>
       </c>
       <c r="B64" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>132116691</v>
       </c>
       <c r="B65" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7542,10 +7542,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132114993</v>
+        <v>132114700</v>
       </c>
       <c r="B66" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7585,10 +7585,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>781633</v>
+        <v>781545</v>
       </c>
       <c r="R66" t="n">
-        <v>7177971</v>
+        <v>7177946</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7648,10 +7648,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132114700</v>
+        <v>132114993</v>
       </c>
       <c r="B67" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7691,10 +7691,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>781545</v>
+        <v>781633</v>
       </c>
       <c r="R67" t="n">
-        <v>7177946</v>
+        <v>7177971</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7757,7 +7757,7 @@
         <v>132116300</v>
       </c>
       <c r="B68" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>132116723</v>
       </c>
       <c r="B69" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>132115643</v>
       </c>
       <c r="B70" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>132115576</v>
       </c>
       <c r="B71" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>132116562</v>
       </c>
       <c r="B72" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>132115737</v>
       </c>
       <c r="B73" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -999,41 +999,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132115035</v>
+        <v>132115712</v>
       </c>
       <c r="B5" t="n">
-        <v>91908</v>
+        <v>99116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781656</v>
+        <v>781622</v>
       </c>
       <c r="R5" t="n">
-        <v>7177972</v>
+        <v>7178004</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på två granlågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1105,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132115712</v>
+        <v>132115952</v>
       </c>
       <c r="B6" t="n">
         <v>99116</v>
@@ -1152,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781622</v>
+        <v>781597</v>
       </c>
       <c r="R6" t="n">
-        <v>7178004</v>
+        <v>7178069</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1211,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132115952</v>
+        <v>132117131</v>
       </c>
       <c r="B7" t="n">
         <v>99116</v>
@@ -1258,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781597</v>
+        <v>781577</v>
       </c>
       <c r="R7" t="n">
-        <v>7178069</v>
+        <v>7178033</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,42 +1317,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132117131</v>
+        <v>132115035</v>
       </c>
       <c r="B8" t="n">
-        <v>99116</v>
+        <v>91908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781577</v>
+        <v>781656</v>
       </c>
       <c r="R8" t="n">
-        <v>7178033</v>
+        <v>7177972</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,6 +1395,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på två granlågor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1859,40 +1859,36 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132115729</v>
+        <v>132115009</v>
       </c>
       <c r="B13" t="n">
-        <v>83173</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1901,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781627</v>
+        <v>781643</v>
       </c>
       <c r="R13" t="n">
-        <v>7178004</v>
+        <v>7177977</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,6 +1933,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,42 +1965,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132116228</v>
+        <v>132116915</v>
       </c>
       <c r="B14" t="n">
-        <v>99116</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2007,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781649</v>
+        <v>781709</v>
       </c>
       <c r="R14" t="n">
-        <v>7178072</v>
+        <v>7178098</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,13 +2046,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska typiska hack i gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2070,36 +2075,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132115009</v>
+        <v>132115729</v>
       </c>
       <c r="B15" t="n">
-        <v>80461</v>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2108,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781643</v>
+        <v>781627</v>
       </c>
       <c r="R15" t="n">
-        <v>7177977</v>
+        <v>7178004</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,11 +2153,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,42 +2180,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132116915</v>
+        <v>132116228</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>99116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2219,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781709</v>
+        <v>781649</v>
       </c>
       <c r="R16" t="n">
-        <v>7178098</v>
+        <v>7178072</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,17 +2261,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>färska typiska hack i gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2286,42 +2286,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132115248</v>
+        <v>132116152</v>
       </c>
       <c r="B17" t="n">
-        <v>99116</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781662</v>
+        <v>781634</v>
       </c>
       <c r="R17" t="n">
-        <v>7177984</v>
+        <v>7178089</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,11 +2364,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,42 +2391,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132114839</v>
+        <v>132116069</v>
       </c>
       <c r="B18" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2440,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781551</v>
+        <v>781642</v>
       </c>
       <c r="R18" t="n">
-        <v>7177965</v>
+        <v>7178096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,13 +2468,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2503,41 +2497,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132116152</v>
+        <v>132115248</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>99116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2545,10 +2540,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781634</v>
+        <v>781662</v>
       </c>
       <c r="R19" t="n">
-        <v>7178089</v>
+        <v>7177984</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,6 +2576,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,38 +2608,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132116069</v>
+        <v>132114839</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>99116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2647,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781642</v>
+        <v>781551</v>
       </c>
       <c r="R20" t="n">
-        <v>7178096</v>
+        <v>7177965</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2685,17 +2689,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -4646,42 +4646,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132115870</v>
+        <v>132116218</v>
       </c>
       <c r="B39" t="n">
-        <v>99116</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781624</v>
+        <v>781643</v>
       </c>
       <c r="R39" t="n">
-        <v>7178022</v>
+        <v>7178078</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,13 +4727,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4752,42 +4756,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132115918</v>
+        <v>132116829</v>
       </c>
       <c r="B40" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4795,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781592</v>
+        <v>781713</v>
       </c>
       <c r="R40" t="n">
-        <v>7178057</v>
+        <v>7178098</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4833,13 +4837,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4858,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132116218</v>
+        <v>132120397</v>
       </c>
       <c r="B41" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4869,16 +4877,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4901,10 +4909,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>781643</v>
+        <v>781702</v>
       </c>
       <c r="R41" t="n">
-        <v>7178078</v>
+        <v>7178053</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4941,14 +4949,14 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -4968,42 +4976,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132116829</v>
+        <v>132115870</v>
       </c>
       <c r="B42" t="n">
-        <v>57953</v>
+        <v>99116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5011,10 +5019,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>781713</v>
+        <v>781624</v>
       </c>
       <c r="R42" t="n">
-        <v>7178098</v>
+        <v>7178022</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,17 +5057,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5078,42 +5082,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132120397</v>
+        <v>132115918</v>
       </c>
       <c r="B43" t="n">
-        <v>57953</v>
+        <v>99116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5121,10 +5125,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>781702</v>
+        <v>781592</v>
       </c>
       <c r="R43" t="n">
-        <v>7178053</v>
+        <v>7178057</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5159,17 +5163,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6043,42 +6043,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132114938</v>
+        <v>132115443</v>
       </c>
       <c r="B52" t="n">
-        <v>99116</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6086,10 +6085,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>781627</v>
+        <v>781657</v>
       </c>
       <c r="R52" t="n">
-        <v>7177962</v>
+        <v>7178001</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6149,10 +6148,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132115443</v>
+        <v>132116712</v>
       </c>
       <c r="B53" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6160,30 +6159,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>781657</v>
+        <v>781744</v>
       </c>
       <c r="R53" t="n">
-        <v>7178001</v>
+        <v>7178073</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6229,13 +6229,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6254,7 +6258,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132116712</v>
+        <v>132114931</v>
       </c>
       <c r="B54" t="n">
         <v>57950</v>
@@ -6287,7 +6291,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6297,10 +6301,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>781744</v>
+        <v>781630</v>
       </c>
       <c r="R54" t="n">
-        <v>7178073</v>
+        <v>7177957</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6337,7 +6341,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>hack i två lågor</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6364,42 +6368,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132114931</v>
+        <v>132114938</v>
       </c>
       <c r="B55" t="n">
-        <v>57950</v>
+        <v>99116</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6407,10 +6411,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>781630</v>
+        <v>781627</v>
       </c>
       <c r="R55" t="n">
-        <v>7177957</v>
+        <v>7177962</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6445,17 +6449,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>hack i två lågor</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6474,10 +6474,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132117193</v>
+        <v>132114915</v>
       </c>
       <c r="B56" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6485,16 +6485,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6505,7 +6505,11 @@
       <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6513,10 +6517,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>781651</v>
+        <v>781609</v>
       </c>
       <c r="R56" t="n">
-        <v>7178085</v>
+        <v>7177970</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6553,14 +6557,14 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>stort bohål i ihålig gammal asp</t>
         </is>
       </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="b">
         <v>0</v>
@@ -6580,42 +6584,41 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132116952</v>
+        <v>132117003</v>
       </c>
       <c r="B57" t="n">
-        <v>99116</v>
+        <v>91908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6623,10 +6626,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>781696</v>
+        <v>781692</v>
       </c>
       <c r="R57" t="n">
-        <v>7178090</v>
+        <v>7178085</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6686,10 +6689,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132114915</v>
+        <v>132115371</v>
       </c>
       <c r="B58" t="n">
-        <v>57950</v>
+        <v>91908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6697,31 +6700,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6729,10 +6731,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>781609</v>
+        <v>781688</v>
       </c>
       <c r="R58" t="n">
-        <v>7177970</v>
+        <v>7178003</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6767,17 +6769,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>stort bohål i ihålig gammal asp</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6796,10 +6794,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132117003</v>
+        <v>132117193</v>
       </c>
       <c r="B59" t="n">
-        <v>91908</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6807,30 +6805,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6838,7 +6833,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>781692</v>
+        <v>781651</v>
       </c>
       <c r="R59" t="n">
         <v>7178085</v>
@@ -6876,13 +6871,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6901,41 +6900,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132115371</v>
+        <v>132116952</v>
       </c>
       <c r="B60" t="n">
-        <v>91908</v>
+        <v>99116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>781688</v>
+        <v>781696</v>
       </c>
       <c r="R60" t="n">
-        <v>7178003</v>
+        <v>7178090</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7006,10 +7006,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132115934</v>
+        <v>132116569</v>
       </c>
       <c r="B61" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7017,30 +7017,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7048,10 +7049,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781602</v>
+        <v>781705</v>
       </c>
       <c r="R61" t="n">
-        <v>7178066</v>
+        <v>7178041</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7086,13 +7087,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7111,10 +7116,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132116569</v>
+        <v>132115934</v>
       </c>
       <c r="B62" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7122,31 +7127,30 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7154,10 +7158,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>781705</v>
+        <v>781602</v>
       </c>
       <c r="R62" t="n">
-        <v>7178041</v>
+        <v>7178066</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7192,17 +7196,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -675,43 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132120235</v>
+        <v>132116162</v>
       </c>
       <c r="B2" t="n">
-        <v>5179</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781536</v>
+        <v>781632</v>
       </c>
       <c r="R2" t="n">
-        <v>7177982</v>
+        <v>7178081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +754,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>typiska gnagspår på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132116162</v>
+        <v>132116033</v>
       </c>
       <c r="B3" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781632</v>
+        <v>781633</v>
       </c>
       <c r="R3" t="n">
-        <v>7178081</v>
+        <v>7178101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,42 +887,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132116033</v>
+        <v>132120235</v>
       </c>
       <c r="B4" t="n">
-        <v>99116</v>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781633</v>
+        <v>781536</v>
       </c>
       <c r="R4" t="n">
-        <v>7178101</v>
+        <v>7177982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>typiska gnagspår på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,42 +999,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132115712</v>
+        <v>132115035</v>
       </c>
       <c r="B5" t="n">
-        <v>99116</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781622</v>
+        <v>781656</v>
       </c>
       <c r="R5" t="n">
-        <v>7178004</v>
+        <v>7177972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1077,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på två granlågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132115952</v>
+        <v>132117131</v>
       </c>
       <c r="B6" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781597</v>
+        <v>781577</v>
       </c>
       <c r="R6" t="n">
-        <v>7178069</v>
+        <v>7178033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132117131</v>
+        <v>132115952</v>
       </c>
       <c r="B7" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781577</v>
+        <v>781597</v>
       </c>
       <c r="R7" t="n">
-        <v>7178033</v>
+        <v>7178069</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,41 +1321,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132115035</v>
+        <v>132115712</v>
       </c>
       <c r="B8" t="n">
-        <v>91908</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1359,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781656</v>
+        <v>781622</v>
       </c>
       <c r="R8" t="n">
-        <v>7177972</v>
+        <v>7178004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,11 +1400,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på två granlågor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,42 +1537,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132115520</v>
+        <v>132115561</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1580,7 +1579,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781655</v>
+        <v>781653</v>
       </c>
       <c r="R10" t="n">
         <v>7178001</v>
@@ -1616,11 +1615,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,41 +1642,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132115561</v>
+        <v>132116022</v>
       </c>
       <c r="B11" t="n">
-        <v>91908</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1690,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781653</v>
+        <v>781624</v>
       </c>
       <c r="R11" t="n">
-        <v>7178001</v>
+        <v>7178093</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132116022</v>
+        <v>132115520</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781624</v>
+        <v>781655</v>
       </c>
       <c r="R12" t="n">
-        <v>7178093</v>
+        <v>7178001</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,6 +1827,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,36 +1859,40 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132115009</v>
+        <v>132115729</v>
       </c>
       <c r="B13" t="n">
-        <v>80461</v>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1897,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781643</v>
+        <v>781627</v>
       </c>
       <c r="R13" t="n">
-        <v>7177977</v>
+        <v>7178004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,11 +1937,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,42 +1964,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132116915</v>
+        <v>132115009</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2008,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781709</v>
+        <v>781643</v>
       </c>
       <c r="R14" t="n">
-        <v>7178098</v>
+        <v>7177977</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,7 +2042,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska typiska hack i gran</t>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,6 +2051,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132115729</v>
+        <v>132116915</v>
       </c>
       <c r="B15" t="n">
-        <v>83173</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,30 +2081,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2117,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781627</v>
+        <v>781709</v>
       </c>
       <c r="R15" t="n">
-        <v>7178004</v>
+        <v>7178098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,13 +2151,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>färska typiska hack i gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>132116228</v>
       </c>
       <c r="B16" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132115248</v>
+        <v>132114839</v>
       </c>
       <c r="B19" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781662</v>
+        <v>781551</v>
       </c>
       <c r="R19" t="n">
-        <v>7177984</v>
+        <v>7177965</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,11 +2576,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132114839</v>
+        <v>132115248</v>
       </c>
       <c r="B20" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2651,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781551</v>
+        <v>781662</v>
       </c>
       <c r="R20" t="n">
-        <v>7177965</v>
+        <v>7177984</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,6 +2682,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,10 +2714,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132115308</v>
+        <v>132117060</v>
       </c>
       <c r="B21" t="n">
-        <v>92096</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,30 +2725,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2756,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781683</v>
+        <v>781577</v>
       </c>
       <c r="R21" t="n">
-        <v>7177990</v>
+        <v>7178033</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,13 +2795,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2819,7 +2824,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132117060</v>
+        <v>132116478</v>
       </c>
       <c r="B22" t="n">
         <v>57953</v>
@@ -2852,7 +2857,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2862,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781577</v>
+        <v>781686</v>
       </c>
       <c r="R22" t="n">
-        <v>7178033</v>
+        <v>7178038</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,14 +2907,14 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>födosökande i granar</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -2929,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132116478</v>
+        <v>132115308</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>92097</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,31 +2945,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2972,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781686</v>
+        <v>781683</v>
       </c>
       <c r="R23" t="n">
-        <v>7178038</v>
+        <v>7177990</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3010,17 +3014,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>födosökande i granar</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>132116701</v>
       </c>
       <c r="B24" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132115704</v>
+        <v>132115101</v>
       </c>
       <c r="B25" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781632</v>
+        <v>781657</v>
       </c>
       <c r="R25" t="n">
-        <v>7178004</v>
+        <v>7177964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,6 +3224,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>rikligt uppe på ett litet stenblock</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3254,7 +3259,7 @@
         <v>132114890</v>
       </c>
       <c r="B26" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3357,10 +3362,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132116490</v>
+        <v>132115704</v>
       </c>
       <c r="B27" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781684</v>
+        <v>781632</v>
       </c>
       <c r="R27" t="n">
-        <v>7178030</v>
+        <v>7178004</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3463,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132115101</v>
+        <v>132116490</v>
       </c>
       <c r="B28" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781657</v>
+        <v>781684</v>
       </c>
       <c r="R28" t="n">
-        <v>7177964</v>
+        <v>7178030</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,11 +3547,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>rikligt uppe på ett litet stenblock</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,7 +3577,7 @@
         <v>132115227</v>
       </c>
       <c r="B29" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>132115000</v>
       </c>
       <c r="B30" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,42 +3896,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132114818</v>
+        <v>132114873</v>
       </c>
       <c r="B32" t="n">
-        <v>99116</v>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3939,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>781549</v>
+        <v>781574</v>
       </c>
       <c r="R32" t="n">
-        <v>7177957</v>
+        <v>7177976</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3975,11 +3974,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4010,7 +4004,7 @@
         <v>132115082</v>
       </c>
       <c r="B33" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4113,41 +4107,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132114873</v>
+        <v>132114818</v>
       </c>
       <c r="B34" t="n">
-        <v>91908</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4155,10 +4150,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781574</v>
+        <v>781549</v>
       </c>
       <c r="R34" t="n">
-        <v>7177976</v>
+        <v>7177957</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4191,6 +4186,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4221,7 +4221,7 @@
         <v>132115061</v>
       </c>
       <c r="B35" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132115209</v>
+        <v>132114726</v>
       </c>
       <c r="B36" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781663</v>
+        <v>781546</v>
       </c>
       <c r="R36" t="n">
-        <v>7177982</v>
+        <v>7177958</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
         <v>132116584</v>
       </c>
       <c r="B37" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4540,10 +4540,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132114726</v>
+        <v>132115209</v>
       </c>
       <c r="B38" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>781546</v>
+        <v>781663</v>
       </c>
       <c r="R38" t="n">
-        <v>7177958</v>
+        <v>7177982</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132116218</v>
+        <v>132116829</v>
       </c>
       <c r="B39" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4657,16 +4657,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781643</v>
+        <v>781713</v>
       </c>
       <c r="R39" t="n">
-        <v>7178078</v>
+        <v>7178098</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4729,14 +4729,14 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132116829</v>
+        <v>132120397</v>
       </c>
       <c r="B40" t="n">
         <v>57953</v>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781713</v>
+        <v>781702</v>
       </c>
       <c r="R40" t="n">
-        <v>7178098</v>
+        <v>7178053</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4866,42 +4866,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132120397</v>
+        <v>132115870</v>
       </c>
       <c r="B41" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>781702</v>
+        <v>781624</v>
       </c>
       <c r="R41" t="n">
-        <v>7178053</v>
+        <v>7178022</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4947,17 +4947,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4976,10 +4972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132115870</v>
+        <v>132115918</v>
       </c>
       <c r="B42" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5019,10 +5015,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>781624</v>
+        <v>781592</v>
       </c>
       <c r="R42" t="n">
-        <v>7178022</v>
+        <v>7178057</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5082,42 +5078,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132115918</v>
+        <v>132116218</v>
       </c>
       <c r="B43" t="n">
-        <v>99116</v>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5125,10 +5121,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>781592</v>
+        <v>781643</v>
       </c>
       <c r="R43" t="n">
-        <v>7178057</v>
+        <v>7178078</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5163,13 +5159,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5188,41 +5188,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132116288</v>
+        <v>132116006</v>
       </c>
       <c r="B44" t="n">
-        <v>91908</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5230,10 +5231,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>781649</v>
+        <v>781602</v>
       </c>
       <c r="R44" t="n">
-        <v>7178072</v>
+        <v>7178094</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,10 +5294,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132115962</v>
+        <v>132115899</v>
       </c>
       <c r="B45" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5336,10 +5337,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>781591</v>
+        <v>781608</v>
       </c>
       <c r="R45" t="n">
-        <v>7178081</v>
+        <v>7178045</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,10 +5400,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132116006</v>
+        <v>132115962</v>
       </c>
       <c r="B46" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5442,10 +5443,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>781602</v>
+        <v>781591</v>
       </c>
       <c r="R46" t="n">
-        <v>7178094</v>
+        <v>7178081</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5505,42 +5506,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132115899</v>
+        <v>132116288</v>
       </c>
       <c r="B47" t="n">
-        <v>99116</v>
+        <v>91909</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>781608</v>
+        <v>781649</v>
       </c>
       <c r="R47" t="n">
-        <v>7178045</v>
+        <v>7178072</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5614,7 +5614,7 @@
         <v>132115856</v>
       </c>
       <c r="B48" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>132115808</v>
       </c>
       <c r="B49" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>132114938</v>
       </c>
       <c r="B55" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6474,42 +6474,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132114915</v>
+        <v>132116952</v>
       </c>
       <c r="B56" t="n">
-        <v>57950</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>781609</v>
+        <v>781696</v>
       </c>
       <c r="R56" t="n">
-        <v>7177970</v>
+        <v>7178090</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6555,17 +6555,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>stort bohål i ihålig gammal asp</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6584,10 +6580,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132117003</v>
+        <v>132117193</v>
       </c>
       <c r="B57" t="n">
-        <v>91908</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6595,30 +6591,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6626,7 +6619,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>781692</v>
+        <v>781651</v>
       </c>
       <c r="R57" t="n">
         <v>7178085</v>
@@ -6664,13 +6657,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6689,10 +6686,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132115371</v>
+        <v>132114915</v>
       </c>
       <c r="B58" t="n">
-        <v>91908</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6700,30 +6697,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6731,10 +6729,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>781688</v>
+        <v>781609</v>
       </c>
       <c r="R58" t="n">
-        <v>7178003</v>
+        <v>7177970</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6769,13 +6767,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>stort bohål i ihålig gammal asp</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6794,10 +6796,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132117193</v>
+        <v>132117003</v>
       </c>
       <c r="B59" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6805,27 +6807,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6833,7 +6838,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>781651</v>
+        <v>781692</v>
       </c>
       <c r="R59" t="n">
         <v>7178085</v>
@@ -6871,17 +6876,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6900,42 +6901,41 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132116952</v>
+        <v>132115371</v>
       </c>
       <c r="B60" t="n">
-        <v>99116</v>
+        <v>91909</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>781696</v>
+        <v>781688</v>
       </c>
       <c r="R60" t="n">
-        <v>7178090</v>
+        <v>7178003</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7006,42 +7006,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132116569</v>
+        <v>132115346</v>
       </c>
       <c r="B61" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7049,10 +7049,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781705</v>
+        <v>781690</v>
       </c>
       <c r="R61" t="n">
-        <v>7178041</v>
+        <v>7177998</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7087,17 +7087,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7221,42 +7217,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132115346</v>
+        <v>132116569</v>
       </c>
       <c r="B63" t="n">
-        <v>99116</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7264,10 +7260,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>781690</v>
+        <v>781705</v>
       </c>
       <c r="R63" t="n">
-        <v>7177998</v>
+        <v>7178041</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7302,13 +7298,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>132114700</v>
       </c>
       <c r="B66" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>132114993</v>
       </c>
       <c r="B67" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>132116300</v>
       </c>
       <c r="B68" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>132115737</v>
       </c>
       <c r="B73" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132120235</v>
+        <v>132115061</v>
       </c>
       <c r="B2" t="n">
-        <v>5179</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781536</v>
+        <v>781656</v>
       </c>
       <c r="R2" t="n">
-        <v>7177982</v>
+        <v>7177972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>typiska gnagspår på gran</t>
+          <t>på samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,42 +785,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132116162</v>
+        <v>132114873</v>
       </c>
       <c r="B3" t="n">
-        <v>99122</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781632</v>
+        <v>781574</v>
       </c>
       <c r="R3" t="n">
-        <v>7178081</v>
+        <v>7177976</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,42 +890,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132116033</v>
+        <v>132115035</v>
       </c>
       <c r="B4" t="n">
-        <v>99122</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>781633</v>
+        <v>781656</v>
       </c>
       <c r="R4" t="n">
-        <v>7178101</v>
+        <v>7177972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på två granlågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132115035</v>
+        <v>132115371</v>
       </c>
       <c r="B5" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781656</v>
+        <v>781688</v>
       </c>
       <c r="R5" t="n">
-        <v>7177972</v>
+        <v>7178003</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på två granlågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,42 +1105,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132117131</v>
+        <v>132115561</v>
       </c>
       <c r="B6" t="n">
-        <v>99122</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1152,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>781577</v>
+        <v>781653</v>
       </c>
       <c r="R6" t="n">
-        <v>7178033</v>
+        <v>7178001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,42 +1210,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132115952</v>
+        <v>132116288</v>
       </c>
       <c r="B7" t="n">
-        <v>99122</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1258,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>781597</v>
+        <v>781649</v>
       </c>
       <c r="R7" t="n">
-        <v>7178069</v>
+        <v>7178072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,42 +1315,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132115712</v>
+        <v>132117003</v>
       </c>
       <c r="B8" t="n">
-        <v>99122</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>781622</v>
+        <v>781692</v>
       </c>
       <c r="R8" t="n">
-        <v>7178004</v>
+        <v>7178085</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132114881</v>
+        <v>132115729</v>
       </c>
       <c r="B9" t="n">
-        <v>57951</v>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,31 +1431,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1470,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>781574</v>
+        <v>781627</v>
       </c>
       <c r="R9" t="n">
-        <v>7177952</v>
+        <v>7178004</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,17 +1500,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1537,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132115561</v>
+        <v>132115308</v>
       </c>
       <c r="B10" t="n">
-        <v>91913</v>
+        <v>92167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1579,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>781653</v>
+        <v>781683</v>
       </c>
       <c r="R10" t="n">
-        <v>7178001</v>
+        <v>7177990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,42 +1630,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132116022</v>
+        <v>132116284</v>
       </c>
       <c r="B11" t="n">
-        <v>99122</v>
+        <v>92367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4877</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Leptoporus mollis/erubescens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>781624</v>
+        <v>781649</v>
       </c>
       <c r="R11" t="n">
-        <v>7178093</v>
+        <v>7178072</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på samma granlåga som ullticka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132115520</v>
+        <v>132115443</v>
       </c>
       <c r="B12" t="n">
-        <v>99122</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,31 +1747,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1791,7 +1778,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>781655</v>
+        <v>781657</v>
       </c>
       <c r="R12" t="n">
         <v>7178001</v>
@@ -1827,11 +1814,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,38 +1841,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132115729</v>
+        <v>132115934</v>
       </c>
       <c r="B13" t="n">
-        <v>83177</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1901,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>781627</v>
+        <v>781602</v>
       </c>
       <c r="R13" t="n">
-        <v>7178004</v>
+        <v>7178066</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,36 +1946,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132115009</v>
+        <v>132116152</v>
       </c>
       <c r="B14" t="n">
-        <v>80463</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2002,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>781643</v>
+        <v>781634</v>
       </c>
       <c r="R14" t="n">
-        <v>7177977</v>
+        <v>7178089</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,11 +2024,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132116915</v>
+        <v>132115643</v>
       </c>
       <c r="B15" t="n">
-        <v>57951</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,31 +2062,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2113,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>781709</v>
+        <v>781644</v>
       </c>
       <c r="R15" t="n">
-        <v>7178098</v>
+        <v>7178004</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2133,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska typiska hack i gran</t>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,6 +2142,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2180,42 +2161,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132116228</v>
+        <v>132115009</v>
       </c>
       <c r="B16" t="n">
-        <v>99122</v>
+        <v>80493</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2223,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>781649</v>
+        <v>781643</v>
       </c>
       <c r="R16" t="n">
-        <v>7178072</v>
+        <v>7177977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,6 +2235,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2286,42 +2267,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132114839</v>
+        <v>132114698</v>
       </c>
       <c r="B17" t="n">
-        <v>99122</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>781551</v>
+        <v>781535</v>
       </c>
       <c r="R17" t="n">
-        <v>7177965</v>
+        <v>7177946</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,13 +2348,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>bohål i tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2392,42 +2377,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132115248</v>
+        <v>132114881</v>
       </c>
       <c r="B18" t="n">
-        <v>99122</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2435,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>781662</v>
+        <v>781574</v>
       </c>
       <c r="R18" t="n">
-        <v>7177984</v>
+        <v>7177952</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,7 +2460,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,7 +2469,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2503,41 +2487,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132116152</v>
+        <v>132114915</v>
       </c>
       <c r="B19" t="n">
-        <v>79329</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2545,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>781634</v>
+        <v>781609</v>
       </c>
       <c r="R19" t="n">
-        <v>7178089</v>
+        <v>7177970</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,13 +2568,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>stort bohål i ihålig gammal asp</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2608,27 +2597,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132116069</v>
+        <v>132114931</v>
       </c>
       <c r="B20" t="n">
-        <v>57954</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2639,7 +2628,11 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2647,10 +2640,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>781642</v>
+        <v>781630</v>
       </c>
       <c r="R20" t="n">
-        <v>7178096</v>
+        <v>7177957</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,14 +2680,14 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>typiska barksprätt på gran</t>
+          <t>hack i två lågor</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2714,41 +2707,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132115308</v>
+        <v>132116218</v>
       </c>
       <c r="B21" t="n">
-        <v>92101</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2756,10 +2750,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>781683</v>
+        <v>781643</v>
       </c>
       <c r="R21" t="n">
-        <v>7177990</v>
+        <v>7178078</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2794,13 +2788,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2819,42 +2817,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132116701</v>
+        <v>132116691</v>
       </c>
       <c r="B22" t="n">
-        <v>99122</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2862,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>781744</v>
+        <v>781724</v>
       </c>
       <c r="R22" t="n">
-        <v>7178071</v>
+        <v>7178057</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2904,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2925,42 +2922,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132115101</v>
+        <v>132116712</v>
       </c>
       <c r="B23" t="n">
-        <v>99122</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2968,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>781657</v>
+        <v>781744</v>
       </c>
       <c r="R23" t="n">
-        <v>7177964</v>
+        <v>7178073</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,7 +3005,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>rikligt uppe på ett litet stenblock</t>
+          <t>typiska hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,7 +3014,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3036,42 +3032,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132114890</v>
+        <v>132116734</v>
       </c>
       <c r="B24" t="n">
-        <v>99122</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3079,10 +3075,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>781609</v>
+        <v>781737</v>
       </c>
       <c r="R24" t="n">
-        <v>7177971</v>
+        <v>7178076</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3117,13 +3113,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>typiska hack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3142,42 +3142,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132115704</v>
+        <v>132116748</v>
       </c>
       <c r="B25" t="n">
-        <v>99122</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>781632</v>
+        <v>781772</v>
       </c>
       <c r="R25" t="n">
-        <v>7178004</v>
+        <v>7178070</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,13 +3223,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3248,42 +3252,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132116490</v>
+        <v>132116915</v>
       </c>
       <c r="B26" t="n">
-        <v>99122</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3291,10 +3295,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>781684</v>
+        <v>781709</v>
       </c>
       <c r="R26" t="n">
-        <v>7178030</v>
+        <v>7178098</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3329,13 +3333,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>färska typiska hack i gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3354,10 +3362,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132117060</v>
+        <v>132114692</v>
       </c>
       <c r="B27" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3385,11 +3393,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3397,10 +3401,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>781577</v>
+        <v>781453</v>
       </c>
       <c r="R27" t="n">
-        <v>7178033</v>
+        <v>7177939</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3464,10 +3468,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132116478</v>
+        <v>132115576</v>
       </c>
       <c r="B28" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,7 +3501,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3507,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>781686</v>
+        <v>781656</v>
       </c>
       <c r="R28" t="n">
-        <v>7178038</v>
+        <v>7178009</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3547,14 +3551,14 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>födosökande i granar</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3574,42 +3578,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132115227</v>
+        <v>132116069</v>
       </c>
       <c r="B29" t="n">
-        <v>99122</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>781674</v>
+        <v>781642</v>
       </c>
       <c r="R29" t="n">
-        <v>7177985</v>
+        <v>7178096</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3655,13 +3655,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3680,42 +3684,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132115000</v>
+        <v>132116133</v>
       </c>
       <c r="B30" t="n">
-        <v>99122</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3723,10 +3727,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>781645</v>
+        <v>781637</v>
       </c>
       <c r="R30" t="n">
-        <v>7177974</v>
+        <v>7178091</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3761,13 +3765,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>observerad på nära håll vid födosök</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3786,10 +3794,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132114873</v>
+        <v>132116371</v>
       </c>
       <c r="B31" t="n">
-        <v>91913</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,30 +3805,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3828,10 +3837,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>781574</v>
+        <v>781671</v>
       </c>
       <c r="R31" t="n">
-        <v>7177976</v>
+        <v>7178082</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3866,13 +3875,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>födosökande, observerad på ca 5 meters håll</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3891,10 +3904,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132116734</v>
+        <v>132116421</v>
       </c>
       <c r="B32" t="n">
-        <v>57951</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3902,16 +3915,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3934,10 +3947,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>781737</v>
+        <v>781686</v>
       </c>
       <c r="R32" t="n">
-        <v>7178076</v>
+        <v>7178038</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3974,7 +3987,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>typiska barksprätt på flera granar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4001,42 +4014,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132115082</v>
+        <v>132116562</v>
       </c>
       <c r="B33" t="n">
-        <v>99122</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4044,10 +4057,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>781661</v>
+        <v>781688</v>
       </c>
       <c r="R33" t="n">
-        <v>7177969</v>
+        <v>7178030</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4082,13 +4095,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>typiska barksprätt</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4107,42 +4124,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132114818</v>
+        <v>132116569</v>
       </c>
       <c r="B34" t="n">
-        <v>99122</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4150,10 +4167,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>781549</v>
+        <v>781705</v>
       </c>
       <c r="R34" t="n">
-        <v>7177957</v>
+        <v>7178041</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4190,16 +4207,15 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ca 1 kvadratmeter med bladrosetter</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4218,10 +4234,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132115061</v>
+        <v>132116723</v>
       </c>
       <c r="B35" t="n">
-        <v>92212</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,30 +4245,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4260,10 +4277,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>781656</v>
+        <v>781744</v>
       </c>
       <c r="R35" t="n">
-        <v>7177972</v>
+        <v>7178073</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4300,7 +4317,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på samma låga som ullticka</t>
+          <t>typiska barksprätt på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4309,7 +4326,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4328,42 +4344,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132114726</v>
+        <v>132116829</v>
       </c>
       <c r="B36" t="n">
-        <v>99122</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4371,10 +4387,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>781546</v>
+        <v>781713</v>
       </c>
       <c r="R36" t="n">
-        <v>7177958</v>
+        <v>7178098</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4409,13 +4425,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4434,42 +4454,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132116584</v>
+        <v>132117060</v>
       </c>
       <c r="B37" t="n">
-        <v>99122</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4477,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>781716</v>
+        <v>781577</v>
       </c>
       <c r="R37" t="n">
-        <v>7178070</v>
+        <v>7178033</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4515,13 +4535,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>typiska barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4540,42 +4564,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132115209</v>
+        <v>132117193</v>
       </c>
       <c r="B38" t="n">
-        <v>99122</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4583,10 +4603,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>781663</v>
+        <v>781651</v>
       </c>
       <c r="R38" t="n">
-        <v>7177982</v>
+        <v>7178085</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4621,13 +4641,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4646,42 +4670,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132115870</v>
+        <v>132120397</v>
       </c>
       <c r="B39" t="n">
-        <v>99122</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4689,10 +4713,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>781624</v>
+        <v>781702</v>
       </c>
       <c r="R39" t="n">
-        <v>7178022</v>
+        <v>7178053</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4727,13 +4751,17 @@
           <t>2026-04-01</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4752,42 +4780,43 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132115918</v>
+        <v>132120235</v>
       </c>
       <c r="B40" t="n">
-        <v>99122</v>
+        <v>5181</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4795,10 +4824,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>781592</v>
+        <v>781536</v>
       </c>
       <c r="R40" t="n">
-        <v>7178057</v>
+        <v>7177982</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4831,6 +4860,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>typiska gnagspår på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4858,42 +4892,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132116829</v>
+        <v>132114700</v>
       </c>
       <c r="B41" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4901,10 +4935,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>781713</v>
+        <v>781545</v>
       </c>
       <c r="R41" t="n">
-        <v>7178098</v>
+        <v>7177946</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4939,17 +4973,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4968,42 +4998,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132120397</v>
+        <v>132114726</v>
       </c>
       <c r="B42" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5011,10 +5041,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>781702</v>
+        <v>781546</v>
       </c>
       <c r="R42" t="n">
-        <v>7178053</v>
+        <v>7177958</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5049,17 +5079,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5078,42 +5104,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132116218</v>
+        <v>132114818</v>
       </c>
       <c r="B43" t="n">
-        <v>57951</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5121,10 +5147,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>781643</v>
+        <v>781549</v>
       </c>
       <c r="R43" t="n">
-        <v>7178078</v>
+        <v>7177957</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5161,7 +5187,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>typiska hack</t>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5170,6 +5196,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5188,10 +5215,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132116006</v>
+        <v>132114839</v>
       </c>
       <c r="B44" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5231,10 +5258,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>781602</v>
+        <v>781551</v>
       </c>
       <c r="R44" t="n">
-        <v>7178094</v>
+        <v>7177965</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5294,10 +5321,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132115899</v>
+        <v>132114890</v>
       </c>
       <c r="B45" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5337,10 +5364,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>781608</v>
+        <v>781609</v>
       </c>
       <c r="R45" t="n">
-        <v>7178045</v>
+        <v>7177971</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,10 +5427,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132115962</v>
+        <v>132114938</v>
       </c>
       <c r="B46" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5443,10 +5470,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>781591</v>
+        <v>781627</v>
       </c>
       <c r="R46" t="n">
-        <v>7178081</v>
+        <v>7177962</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5506,41 +5533,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132116288</v>
+        <v>132114993</v>
       </c>
       <c r="B47" t="n">
-        <v>91913</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5548,10 +5576,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>781649</v>
+        <v>781633</v>
       </c>
       <c r="R47" t="n">
-        <v>7178072</v>
+        <v>7177971</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5611,42 +5639,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132116133</v>
+        <v>132115000</v>
       </c>
       <c r="B48" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5654,10 +5682,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>781637</v>
+        <v>781645</v>
       </c>
       <c r="R48" t="n">
-        <v>7178091</v>
+        <v>7177974</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5692,17 +5720,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>observerad på nära håll vid födosök</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5721,42 +5745,42 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132116371</v>
+        <v>132115082</v>
       </c>
       <c r="B49" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5764,10 +5788,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>781671</v>
+        <v>781661</v>
       </c>
       <c r="R49" t="n">
-        <v>7178082</v>
+        <v>7177969</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5802,17 +5826,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>födosökande, observerad på ca 5 meters håll</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5831,10 +5851,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132115856</v>
+        <v>132115101</v>
       </c>
       <c r="B50" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5874,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>781632</v>
+        <v>781657</v>
       </c>
       <c r="R50" t="n">
-        <v>7178016</v>
+        <v>7177964</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5910,6 +5930,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>rikligt uppe på ett litet stenblock</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5937,10 +5962,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132115808</v>
+        <v>132115209</v>
       </c>
       <c r="B51" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5980,10 +6005,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>781627</v>
+        <v>781663</v>
       </c>
       <c r="R51" t="n">
-        <v>7178015</v>
+        <v>7177982</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6043,42 +6068,42 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132116712</v>
+        <v>132115227</v>
       </c>
       <c r="B52" t="n">
-        <v>57951</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6086,10 +6111,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>781744</v>
+        <v>781674</v>
       </c>
       <c r="R52" t="n">
-        <v>7178073</v>
+        <v>7177985</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6124,17 +6149,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>typiska hack</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6153,10 +6174,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132114938</v>
+        <v>132115248</v>
       </c>
       <c r="B53" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6196,10 +6217,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>781627</v>
+        <v>781662</v>
       </c>
       <c r="R53" t="n">
-        <v>7177962</v>
+        <v>7177984</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6232,6 +6253,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>ca 1 kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6259,41 +6285,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132115443</v>
+        <v>132115346</v>
       </c>
       <c r="B54" t="n">
-        <v>79329</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6301,10 +6328,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>781657</v>
+        <v>781690</v>
       </c>
       <c r="R54" t="n">
-        <v>7178001</v>
+        <v>7177998</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6364,42 +6391,42 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132114931</v>
+        <v>132115520</v>
       </c>
       <c r="B55" t="n">
-        <v>57951</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6407,10 +6434,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>781630</v>
+        <v>781655</v>
       </c>
       <c r="R55" t="n">
-        <v>7177957</v>
+        <v>7178001</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6447,7 +6474,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>hack i två lågor</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,6 +6483,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6474,41 +6502,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132117003</v>
+        <v>132115704</v>
       </c>
       <c r="B56" t="n">
-        <v>91913</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6516,10 +6545,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>781692</v>
+        <v>781632</v>
       </c>
       <c r="R56" t="n">
-        <v>7178085</v>
+        <v>7178004</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6579,41 +6608,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132115371</v>
+        <v>132115712</v>
       </c>
       <c r="B57" t="n">
-        <v>91913</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6621,10 +6651,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>781688</v>
+        <v>781622</v>
       </c>
       <c r="R57" t="n">
-        <v>7178003</v>
+        <v>7178004</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6684,38 +6714,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132117193</v>
+        <v>132115737</v>
       </c>
       <c r="B58" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6723,10 +6757,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>781651</v>
+        <v>781633</v>
       </c>
       <c r="R58" t="n">
-        <v>7178085</v>
+        <v>7178011</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6761,17 +6795,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6790,42 +6820,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132114915</v>
+        <v>132115808</v>
       </c>
       <c r="B59" t="n">
-        <v>57951</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6833,10 +6863,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>781609</v>
+        <v>781627</v>
       </c>
       <c r="R59" t="n">
-        <v>7177970</v>
+        <v>7178015</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6871,17 +6901,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>stort bohål i ihålig gammal asp</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6900,10 +6926,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132116952</v>
+        <v>132115856</v>
       </c>
       <c r="B60" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6943,10 +6969,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>781696</v>
+        <v>781632</v>
       </c>
       <c r="R60" t="n">
-        <v>7178090</v>
+        <v>7178016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7006,41 +7032,42 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132115934</v>
+        <v>132115870</v>
       </c>
       <c r="B61" t="n">
-        <v>79329</v>
+        <v>99195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7048,10 +7075,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>781602</v>
+        <v>781624</v>
       </c>
       <c r="R61" t="n">
-        <v>7178066</v>
+        <v>7178022</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7111,42 +7138,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132116569</v>
+        <v>132115899</v>
       </c>
       <c r="B62" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7154,10 +7181,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>781705</v>
+        <v>781608</v>
       </c>
       <c r="R62" t="n">
-        <v>7178041</v>
+        <v>7178045</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7192,17 +7219,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7221,10 +7244,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132115346</v>
+        <v>132115918</v>
       </c>
       <c r="B63" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7264,10 +7287,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>781690</v>
+        <v>781592</v>
       </c>
       <c r="R63" t="n">
-        <v>7177998</v>
+        <v>7178057</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7327,10 +7350,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132114993</v>
+        <v>132115952</v>
       </c>
       <c r="B64" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7370,10 +7393,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>781633</v>
+        <v>781597</v>
       </c>
       <c r="R64" t="n">
-        <v>7177971</v>
+        <v>7178069</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7433,10 +7456,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132114700</v>
+        <v>132115962</v>
       </c>
       <c r="B65" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7476,10 +7499,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>781545</v>
+        <v>781591</v>
       </c>
       <c r="R65" t="n">
-        <v>7177946</v>
+        <v>7178081</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7539,42 +7562,42 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132114698</v>
+        <v>132116006</v>
       </c>
       <c r="B66" t="n">
-        <v>57951</v>
+        <v>99195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7582,10 +7605,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>781535</v>
+        <v>781602</v>
       </c>
       <c r="R66" t="n">
-        <v>7177946</v>
+        <v>7178094</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7620,17 +7643,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>bohål i tall</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7649,42 +7668,42 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132116691</v>
+        <v>132116022</v>
       </c>
       <c r="B67" t="n">
-        <v>57951</v>
+        <v>99195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7692,10 +7711,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>781724</v>
+        <v>781624</v>
       </c>
       <c r="R67" t="n">
-        <v>7178057</v>
+        <v>7178093</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7736,6 +7755,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7754,10 +7774,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132116300</v>
+        <v>132116033</v>
       </c>
       <c r="B68" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7797,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>781667</v>
+        <v>781633</v>
       </c>
       <c r="R68" t="n">
-        <v>7178072</v>
+        <v>7178101</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7860,42 +7880,42 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132116723</v>
+        <v>132116162</v>
       </c>
       <c r="B69" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7903,10 +7923,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>781744</v>
+        <v>781632</v>
       </c>
       <c r="R69" t="n">
-        <v>7178073</v>
+        <v>7178081</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7941,17 +7961,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7970,41 +7986,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132115643</v>
+        <v>132116228</v>
       </c>
       <c r="B70" t="n">
-        <v>80434</v>
+        <v>99195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8012,10 +8029,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>781644</v>
+        <v>781649</v>
       </c>
       <c r="R70" t="n">
-        <v>7178004</v>
+        <v>7178072</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8048,11 +8065,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>på en gammal sälg</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8080,42 +8092,42 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132115576</v>
+        <v>132116300</v>
       </c>
       <c r="B71" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8123,10 +8135,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>781656</v>
+        <v>781667</v>
       </c>
       <c r="R71" t="n">
-        <v>7178009</v>
+        <v>7178072</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8161,17 +8173,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>typiska barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8190,42 +8198,42 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132116562</v>
+        <v>132116490</v>
       </c>
       <c r="B72" t="n">
-        <v>57954</v>
+        <v>99195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8233,7 +8241,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>781688</v>
+        <v>781684</v>
       </c>
       <c r="R72" t="n">
         <v>7178030</v>
@@ -8271,17 +8279,13 @@
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>typiska barksprätt</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8300,10 +8304,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132115737</v>
+        <v>132116584</v>
       </c>
       <c r="B73" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8343,10 +8347,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>781633</v>
+        <v>781716</v>
       </c>
       <c r="R73" t="n">
-        <v>7178011</v>
+        <v>7178070</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8403,6 +8407,324 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132116701</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Nördberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>781744</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7178071</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132116952</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Nördberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>781696</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7178090</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132117131</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Nördberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>781577</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7178033</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57232-2025 artfynd.xlsx
+++ b/artfynd/A 57232-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115061</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114873</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115035</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115371</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115561</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116288</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132117003</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115729</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1627,6 +1672,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115308</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1733,6 +1783,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116284</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115443</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115934</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2048,6 +2113,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116152</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2158,6 +2228,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115643</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2264,6 +2339,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115009</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114698</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2484,6 +2569,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114881</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2594,6 +2684,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114915</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2704,6 +2799,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114931</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2814,6 +2914,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116218</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116691</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3029,6 +3139,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116712</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3139,6 +3254,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116734</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3249,6 +3369,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116748</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3359,6 +3484,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116915</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3465,6 +3595,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114692</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3575,6 +3710,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115576</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3681,6 +3821,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116069</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3791,6 +3936,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116133</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3901,6 +4051,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116371</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4011,6 +4166,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116421</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4121,6 +4281,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116562</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4231,6 +4396,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116569</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4341,6 +4511,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116723</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4451,6 +4626,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116829</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4561,6 +4741,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132117060</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4667,6 +4852,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132117193</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4777,6 +4967,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120397</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4889,6 +5084,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120235</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4995,6 +5195,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114700</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5101,6 +5306,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114726</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5212,6 +5422,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114818</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5318,6 +5533,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114839</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5424,6 +5644,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114890</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5530,6 +5755,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114938</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5636,6 +5866,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132114993</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5742,6 +5977,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115000</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5848,6 +6088,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115082</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5959,6 +6204,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115101</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6065,6 +6315,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115209</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6171,6 +6426,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115227</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6282,6 +6542,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115248</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6388,6 +6653,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115346</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6499,6 +6769,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115520</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6605,6 +6880,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115704</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6711,6 +6991,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115712</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6817,6 +7102,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115737</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6923,6 +7213,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115808</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7029,6 +7324,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115856</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7135,6 +7435,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115870</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7241,6 +7546,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115899</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7347,6 +7657,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115918</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7453,6 +7768,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115952</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7559,6 +7879,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132115962</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7665,6 +7990,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116006</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7771,6 +8101,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116022</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7877,6 +8212,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116033</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7983,6 +8323,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116162</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8089,6 +8434,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116228</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8195,6 +8545,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116300</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8301,6 +8656,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116490</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8407,6 +8767,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116584</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8513,6 +8878,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116701</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8619,6 +8989,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132116952</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8725,8 +9100,90 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132117131</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>